--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -5619,40 +5619,40 @@
     <t xml:space="preserve">Mark registers 213-222 as unsupported</t>
   </si>
   <si>
+    <t xml:space="preserve">Add registers for VE.Bus Relay Test OK state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add registers for missing Lynx alarms (registers 327 and 328)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add registers for VE.Bus Nominal inverter power (registers 130 to 136)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rev 53</t>
   </si>
   <si>
-    <t xml:space="preserve">Add registers for VE.Bus Relay Test OK state</t>
+    <t xml:space="preserve">Add register 3836 for total EV Charger energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add 32-bit registers for maximum feed-in power and maximum discharge power (registers 2720 and 2722)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add registers for reading/writing custom names of several services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add register for reading/writing system name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add registers for microgrid operation switching (registers 232-234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add registers for microgrid capacity (240-246)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add registers for disabling PV on VE.Bus and Multi-RS systems (register 2724 and 4929)</t>
   </si>
   <si>
     <t xml:space="preserve">Add reserved ranges to system range (to allow fetching blocks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add registers for missing Lynx alarms (registers 327 and 328)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add registers for VE.Bus Nominal inverter power (registers 130 to 136)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add register 3836 for total EV Charger energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add 32-bit registers for maximum feed-in power and maximum discharge power (registers 2720 and 2722)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add registers for reading/writing custom names of several services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add register for reading/writing system name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add registers for microgrid operation switching (registers 232-234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add registers for microgrid capacity (240-246)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add registers for disabling PV on VE.Bus and Multi-RS systems (register 2724 and 4929)</t>
   </si>
 </sst>
 </file>
@@ -5845,7 +5845,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5952,10 +5952,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -20618,7 +20614,7 @@
       <c r="E492" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I492" s="27"/>
+      <c r="I492" s="3"/>
     </row>
     <row r="493" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
@@ -21061,7 +21057,7 @@
       <c r="H507" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I507" s="28"/>
+      <c r="I507" s="27"/>
     </row>
     <row r="508" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
@@ -24309,7 +24305,7 @@
       <c r="A625" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B625" s="29" t="s">
+      <c r="B625" s="28" t="s">
         <v>1205</v>
       </c>
       <c r="C625" s="1" t="n">
@@ -24341,7 +24337,7 @@
       <c r="A626" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B626" s="29" t="s">
+      <c r="B626" s="28" t="s">
         <v>1210</v>
       </c>
       <c r="C626" s="1" t="n">
@@ -24356,7 +24352,7 @@
       <c r="F626" s="3" t="s">
         <v>1212</v>
       </c>
-      <c r="G626" s="30" t="s">
+      <c r="G626" s="29" t="s">
         <v>1213</v>
       </c>
       <c r="H626" s="1" t="s">
@@ -24373,7 +24369,7 @@
       <c r="A627" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B627" s="29" t="s">
+      <c r="B627" s="28" t="s">
         <v>1215</v>
       </c>
       <c r="C627" s="1" t="n">
@@ -24402,7 +24398,7 @@
       <c r="A628" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B628" s="29" t="s">
+      <c r="B628" s="28" t="s">
         <v>1218</v>
       </c>
       <c r="C628" s="1" t="n">
@@ -24423,7 +24419,7 @@
       <c r="H628" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I628" s="29" t="s">
+      <c r="I628" s="28" t="s">
         <v>1221</v>
       </c>
       <c r="J628" s="1" t="s">
@@ -24434,7 +24430,7 @@
       <c r="A629" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B629" s="29" t="s">
+      <c r="B629" s="28" t="s">
         <v>1222</v>
       </c>
       <c r="C629" s="1" t="n">
@@ -24463,7 +24459,7 @@
       <c r="A630" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B630" s="29" t="s">
+      <c r="B630" s="28" t="s">
         <v>117</v>
       </c>
       <c r="C630" s="23" t="s">
@@ -24477,7 +24473,7 @@
       <c r="A631" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B631" s="29" t="s">
+      <c r="B631" s="28" t="s">
         <v>436</v>
       </c>
       <c r="C631" s="1" t="n">
@@ -25724,7 +25720,7 @@
       <c r="E677" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F677" s="31" t="s">
+      <c r="F677" s="30" t="s">
         <v>747</v>
       </c>
       <c r="G677" s="1" t="s">
@@ -25782,7 +25778,7 @@
       <c r="E679" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F679" s="32" t="s">
+      <c r="F679" s="31" t="s">
         <v>1304</v>
       </c>
       <c r="G679" s="1" t="s">
@@ -25808,7 +25804,7 @@
       <c r="E680" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F680" s="32" t="s">
+      <c r="F680" s="31" t="s">
         <v>1304</v>
       </c>
       <c r="G680" s="1" t="s">
@@ -26299,13 +26295,13 @@
       <c r="C699" s="1" t="n">
         <v>3924</v>
       </c>
-      <c r="D699" s="33" t="s">
+      <c r="D699" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E699" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F699" s="32" t="s">
+      <c r="F699" s="31" t="s">
         <v>140</v>
       </c>
       <c r="G699" s="1" t="s">
@@ -26328,13 +26324,13 @@
       <c r="C700" s="1" t="n">
         <v>3926</v>
       </c>
-      <c r="D700" s="33" t="s">
+      <c r="D700" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E700" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F700" s="32" t="s">
+      <c r="F700" s="31" t="s">
         <v>140</v>
       </c>
       <c r="G700" s="1" t="s">
@@ -26357,13 +26353,13 @@
       <c r="C701" s="1" t="n">
         <v>3928</v>
       </c>
-      <c r="D701" s="33" t="s">
+      <c r="D701" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E701" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F701" s="32" t="s">
+      <c r="F701" s="31" t="s">
         <v>140</v>
       </c>
       <c r="G701" s="1" t="s">
@@ -26524,7 +26520,7 @@
       <c r="C708" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="D708" s="33" t="s">
+      <c r="D708" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E708" s="22" t="n">
@@ -26553,7 +26549,7 @@
       <c r="C709" s="22" t="n">
         <v>4001</v>
       </c>
-      <c r="D709" s="33" t="s">
+      <c r="D709" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E709" s="22" t="n">
@@ -26582,7 +26578,7 @@
       <c r="C710" s="22" t="n">
         <v>4002</v>
       </c>
-      <c r="D710" s="33" t="s">
+      <c r="D710" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E710" s="22" t="n">
@@ -26611,7 +26607,7 @@
       <c r="C711" s="22" t="n">
         <v>4003</v>
       </c>
-      <c r="D711" s="33" t="s">
+      <c r="D711" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E711" s="22" t="n">
@@ -26640,7 +26636,7 @@
       <c r="C712" s="22" t="n">
         <v>4004</v>
       </c>
-      <c r="D712" s="33" t="s">
+      <c r="D712" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E712" s="22" t="n">
@@ -26669,7 +26665,7 @@
       <c r="C713" s="22" t="n">
         <v>4006</v>
       </c>
-      <c r="D713" s="33" t="s">
+      <c r="D713" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E713" s="22" t="n">
@@ -26698,7 +26694,7 @@
       <c r="C714" s="22" t="n">
         <v>4007</v>
       </c>
-      <c r="D714" s="33" t="s">
+      <c r="D714" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E714" s="22" t="n">
@@ -26727,7 +26723,7 @@
       <c r="C715" s="22" t="n">
         <v>4008</v>
       </c>
-      <c r="D715" s="33" t="s">
+      <c r="D715" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E715" s="22" t="n">
@@ -26756,7 +26752,7 @@
       <c r="C716" s="22" t="n">
         <v>4009</v>
       </c>
-      <c r="D716" s="33" t="s">
+      <c r="D716" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E716" s="22" t="n">
@@ -26785,7 +26781,7 @@
       <c r="C717" s="22" t="n">
         <v>4010</v>
       </c>
-      <c r="D717" s="33" t="s">
+      <c r="D717" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E717" s="22" t="n">
@@ -26814,7 +26810,7 @@
       <c r="C718" s="22" t="n">
         <v>4011</v>
       </c>
-      <c r="D718" s="33" t="s">
+      <c r="D718" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E718" s="22" t="n">
@@ -26843,7 +26839,7 @@
       <c r="C719" s="22" t="n">
         <v>4100</v>
       </c>
-      <c r="D719" s="33" t="s">
+      <c r="D719" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E719" s="22" t="n">
@@ -26872,7 +26868,7 @@
       <c r="C720" s="22" t="n">
         <v>4101</v>
       </c>
-      <c r="D720" s="33" t="s">
+      <c r="D720" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E720" s="22" t="n">
@@ -26901,7 +26897,7 @@
       <c r="C721" s="22" t="n">
         <v>4102</v>
       </c>
-      <c r="D721" s="33" t="s">
+      <c r="D721" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E721" s="22" t="n">
@@ -26930,7 +26926,7 @@
       <c r="C722" s="22" t="n">
         <v>4103</v>
       </c>
-      <c r="D722" s="33" t="s">
+      <c r="D722" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E722" s="22" t="n">
@@ -26959,7 +26955,7 @@
       <c r="C723" s="22" t="n">
         <v>4104</v>
       </c>
-      <c r="D723" s="33" t="s">
+      <c r="D723" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E723" s="22" t="n">
@@ -26988,7 +26984,7 @@
       <c r="C724" s="22" t="n">
         <v>4106</v>
       </c>
-      <c r="D724" s="33" t="s">
+      <c r="D724" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E724" s="22" t="n">
@@ -27017,7 +27013,7 @@
       <c r="C725" s="22" t="n">
         <v>4107</v>
       </c>
-      <c r="D725" s="33" t="s">
+      <c r="D725" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E725" s="22" t="n">
@@ -27046,7 +27042,7 @@
       <c r="C726" s="22" t="n">
         <v>4108</v>
       </c>
-      <c r="D726" s="33" t="s">
+      <c r="D726" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E726" s="22" t="n">
@@ -27075,7 +27071,7 @@
       <c r="C727" s="22" t="n">
         <v>4109</v>
       </c>
-      <c r="D727" s="33" t="s">
+      <c r="D727" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E727" s="22" t="n">
@@ -27104,7 +27100,7 @@
       <c r="C728" s="22" t="n">
         <v>4110</v>
       </c>
-      <c r="D728" s="33" t="s">
+      <c r="D728" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E728" s="22" t="n">
@@ -27133,7 +27129,7 @@
       <c r="C729" s="22" t="n">
         <v>4111</v>
       </c>
-      <c r="D729" s="33" t="s">
+      <c r="D729" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E729" s="22" t="n">
@@ -27162,7 +27158,7 @@
       <c r="C730" s="22" t="n">
         <v>4112</v>
       </c>
-      <c r="D730" s="33" t="s">
+      <c r="D730" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E730" s="22" t="n">
@@ -27191,7 +27187,7 @@
       <c r="C731" s="22" t="n">
         <v>4113</v>
       </c>
-      <c r="D731" s="33" t="s">
+      <c r="D731" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E731" s="22" t="n">
@@ -27220,7 +27216,7 @@
       <c r="C732" s="22" t="n">
         <v>4114</v>
       </c>
-      <c r="D732" s="33" t="s">
+      <c r="D732" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E732" s="22" t="n">
@@ -27249,7 +27245,7 @@
       <c r="C733" s="22" t="n">
         <v>4115</v>
       </c>
-      <c r="D733" s="33" t="s">
+      <c r="D733" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E733" s="22" t="n">
@@ -27278,7 +27274,7 @@
       <c r="C734" s="22" t="n">
         <v>4116</v>
       </c>
-      <c r="D734" s="33" t="s">
+      <c r="D734" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E734" s="22" t="n">
@@ -27307,7 +27303,7 @@
       <c r="C735" s="22" t="n">
         <v>4117</v>
       </c>
-      <c r="D735" s="33" t="s">
+      <c r="D735" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E735" s="22" t="n">
@@ -27336,7 +27332,7 @@
       <c r="C736" s="22" t="n">
         <v>4118</v>
       </c>
-      <c r="D736" s="33" t="s">
+      <c r="D736" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E736" s="22" t="n">
@@ -27365,7 +27361,7 @@
       <c r="C737" s="22" t="n">
         <v>4119</v>
       </c>
-      <c r="D737" s="33" t="s">
+      <c r="D737" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E737" s="22" t="n">
@@ -27394,7 +27390,7 @@
       <c r="C738" s="22" t="n">
         <v>4120</v>
       </c>
-      <c r="D738" s="33" t="s">
+      <c r="D738" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E738" s="22" t="n">
@@ -27423,7 +27419,7 @@
       <c r="C739" s="22" t="s">
         <v>1335</v>
       </c>
-      <c r="D739" s="33"/>
+      <c r="D739" s="32"/>
       <c r="E739" s="22"/>
       <c r="G739" s="22" t="s">
         <v>117</v>
@@ -27439,7 +27435,7 @@
       <c r="C740" s="22" t="n">
         <v>4220</v>
       </c>
-      <c r="D740" s="33" t="s">
+      <c r="D740" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E740" s="22"/>
@@ -27460,7 +27456,7 @@
       <c r="C741" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="D741" s="33" t="s">
+      <c r="D741" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E741" s="22" t="n">
@@ -27489,7 +27485,7 @@
       <c r="C742" s="22" t="n">
         <v>4201</v>
       </c>
-      <c r="D742" s="33" t="s">
+      <c r="D742" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E742" s="22" t="n">
@@ -27518,7 +27514,7 @@
       <c r="C743" s="22" t="n">
         <v>4202</v>
       </c>
-      <c r="D743" s="33" t="s">
+      <c r="D743" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E743" s="22" t="n">
@@ -27547,7 +27543,7 @@
       <c r="C744" s="22" t="n">
         <v>4203</v>
       </c>
-      <c r="D744" s="33" t="s">
+      <c r="D744" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E744" s="22" t="n">
@@ -27576,7 +27572,7 @@
       <c r="C745" s="22" t="n">
         <v>4204</v>
       </c>
-      <c r="D745" s="33" t="s">
+      <c r="D745" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E745" s="22" t="n">
@@ -27605,7 +27601,7 @@
       <c r="C746" s="22" t="n">
         <v>4206</v>
       </c>
-      <c r="D746" s="33" t="s">
+      <c r="D746" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E746" s="22" t="n">
@@ -27634,7 +27630,7 @@
       <c r="C747" s="22" t="n">
         <v>4207</v>
       </c>
-      <c r="D747" s="33" t="s">
+      <c r="D747" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E747" s="22" t="n">
@@ -27663,7 +27659,7 @@
       <c r="C748" s="22" t="n">
         <v>4208</v>
       </c>
-      <c r="D748" s="33" t="s">
+      <c r="D748" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E748" s="22" t="n">
@@ -27692,7 +27688,7 @@
       <c r="C749" s="22" t="n">
         <v>4209</v>
       </c>
-      <c r="D749" s="33" t="s">
+      <c r="D749" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E749" s="22" t="n">
@@ -27721,7 +27717,7 @@
       <c r="C750" s="22" t="n">
         <v>4210</v>
       </c>
-      <c r="D750" s="33" t="s">
+      <c r="D750" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E750" s="22" t="n">
@@ -27750,7 +27746,7 @@
       <c r="C751" s="22" t="n">
         <v>4211</v>
       </c>
-      <c r="D751" s="33" t="s">
+      <c r="D751" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E751" s="22" t="n">
@@ -27779,7 +27775,7 @@
       <c r="C752" s="24" t="s">
         <v>1337</v>
       </c>
-      <c r="D752" s="33"/>
+      <c r="D752" s="32"/>
       <c r="E752" s="22"/>
       <c r="G752" s="22" t="s">
         <v>117</v>
@@ -27795,7 +27791,7 @@
       <c r="C753" s="22" t="n">
         <v>4220</v>
       </c>
-      <c r="D753" s="33" t="s">
+      <c r="D753" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E753" s="22"/>
@@ -27816,7 +27812,7 @@
       <c r="C754" s="22" t="n">
         <v>4300</v>
       </c>
-      <c r="D754" s="33" t="s">
+      <c r="D754" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E754" s="22" t="n">
@@ -27845,7 +27841,7 @@
       <c r="C755" s="22" t="n">
         <v>4301</v>
       </c>
-      <c r="D755" s="33" t="s">
+      <c r="D755" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E755" s="22" t="n">
@@ -27874,7 +27870,7 @@
       <c r="C756" s="22" t="n">
         <v>4302</v>
       </c>
-      <c r="D756" s="33" t="s">
+      <c r="D756" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E756" s="22" t="n">
@@ -27903,7 +27899,7 @@
       <c r="C757" s="22" t="n">
         <v>4303</v>
       </c>
-      <c r="D757" s="33" t="s">
+      <c r="D757" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E757" s="22" t="n">
@@ -27932,7 +27928,7 @@
       <c r="C758" s="22" t="n">
         <v>4304</v>
       </c>
-      <c r="D758" s="33" t="s">
+      <c r="D758" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E758" s="22" t="n">
@@ -27961,7 +27957,7 @@
       <c r="C759" s="22" t="n">
         <v>4306</v>
       </c>
-      <c r="D759" s="33" t="s">
+      <c r="D759" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E759" s="22" t="n">
@@ -27990,7 +27986,7 @@
       <c r="C760" s="22" t="n">
         <v>4307</v>
       </c>
-      <c r="D760" s="33" t="s">
+      <c r="D760" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E760" s="22" t="n">
@@ -28019,7 +28015,7 @@
       <c r="C761" s="22" t="n">
         <v>4308</v>
       </c>
-      <c r="D761" s="33" t="s">
+      <c r="D761" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E761" s="22" t="n">
@@ -28048,7 +28044,7 @@
       <c r="C762" s="22" t="n">
         <v>4309</v>
       </c>
-      <c r="D762" s="33" t="s">
+      <c r="D762" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E762" s="22" t="n">
@@ -28077,7 +28073,7 @@
       <c r="C763" s="22" t="n">
         <v>4310</v>
       </c>
-      <c r="D763" s="33" t="s">
+      <c r="D763" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E763" s="22" t="n">
@@ -28106,7 +28102,7 @@
       <c r="C764" s="22" t="n">
         <v>4311</v>
       </c>
-      <c r="D764" s="33" t="s">
+      <c r="D764" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E764" s="22" t="n">
@@ -28135,7 +28131,7 @@
       <c r="C765" s="24" t="s">
         <v>1341</v>
       </c>
-      <c r="D765" s="33"/>
+      <c r="D765" s="32"/>
       <c r="E765" s="22"/>
       <c r="G765" s="22" t="s">
         <v>117</v>
@@ -28151,7 +28147,7 @@
       <c r="C766" s="22" t="n">
         <v>4320</v>
       </c>
-      <c r="D766" s="33" t="s">
+      <c r="D766" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E766" s="22"/>
@@ -28172,7 +28168,7 @@
       <c r="C767" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="D767" s="33" t="s">
+      <c r="D767" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E767" s="22" t="n">
@@ -28201,7 +28197,7 @@
       <c r="C768" s="22" t="n">
         <v>4401</v>
       </c>
-      <c r="D768" s="33" t="s">
+      <c r="D768" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E768" s="22" t="n">
@@ -28230,7 +28226,7 @@
       <c r="C769" s="22" t="n">
         <v>4402</v>
       </c>
-      <c r="D769" s="33" t="s">
+      <c r="D769" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E769" s="22" t="n">
@@ -28259,7 +28255,7 @@
       <c r="C770" s="22" t="n">
         <v>4403</v>
       </c>
-      <c r="D770" s="33" t="s">
+      <c r="D770" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E770" s="22" t="n">
@@ -28288,7 +28284,7 @@
       <c r="C771" s="22" t="n">
         <v>4404</v>
       </c>
-      <c r="D771" s="33" t="s">
+      <c r="D771" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E771" s="22" t="n">
@@ -28317,7 +28313,7 @@
       <c r="C772" s="22" t="n">
         <v>4406</v>
       </c>
-      <c r="D772" s="33" t="s">
+      <c r="D772" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E772" s="22" t="n">
@@ -28346,7 +28342,7 @@
       <c r="C773" s="22" t="n">
         <v>4408</v>
       </c>
-      <c r="D773" s="33" t="s">
+      <c r="D773" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E773" s="22" t="n">
@@ -28375,7 +28371,7 @@
       <c r="C774" s="22" t="n">
         <v>4409</v>
       </c>
-      <c r="D774" s="33" t="s">
+      <c r="D774" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E774" s="22" t="n">
@@ -28404,7 +28400,7 @@
       <c r="C775" s="22" t="n">
         <v>4410</v>
       </c>
-      <c r="D775" s="33" t="s">
+      <c r="D775" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E775" s="22" t="n">
@@ -28433,7 +28429,7 @@
       <c r="C776" s="22" t="n">
         <v>4411</v>
       </c>
-      <c r="D776" s="33" t="s">
+      <c r="D776" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E776" s="22" t="n">
@@ -28462,7 +28458,7 @@
       <c r="C777" s="22" t="n">
         <v>4412</v>
       </c>
-      <c r="D777" s="33" t="s">
+      <c r="D777" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E777" s="22" t="n">
@@ -28491,7 +28487,7 @@
       <c r="C778" s="22" t="n">
         <v>4413</v>
       </c>
-      <c r="D778" s="33" t="s">
+      <c r="D778" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E778" s="22" t="n">
@@ -28520,7 +28516,7 @@
       <c r="C779" s="24" t="s">
         <v>1344</v>
       </c>
-      <c r="D779" s="33"/>
+      <c r="D779" s="32"/>
       <c r="E779" s="22"/>
       <c r="G779" s="22" t="s">
         <v>117</v>
@@ -28536,7 +28532,7 @@
       <c r="C780" s="22" t="n">
         <v>4420</v>
       </c>
-      <c r="D780" s="33" t="s">
+      <c r="D780" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E780" s="22"/>
@@ -28557,7 +28553,7 @@
       <c r="C781" s="22" t="n">
         <v>4500</v>
       </c>
-      <c r="D781" s="33" t="s">
+      <c r="D781" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E781" s="22" t="n">
@@ -28586,7 +28582,7 @@
       <c r="C782" s="22" t="n">
         <v>4501</v>
       </c>
-      <c r="D782" s="33" t="s">
+      <c r="D782" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E782" s="22" t="n">
@@ -28615,7 +28611,7 @@
       <c r="C783" s="22" t="n">
         <v>4502</v>
       </c>
-      <c r="D783" s="33" t="s">
+      <c r="D783" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E783" s="22" t="n">
@@ -28644,7 +28640,7 @@
       <c r="C784" s="22" t="n">
         <v>4503</v>
       </c>
-      <c r="D784" s="33" t="s">
+      <c r="D784" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E784" s="22" t="n">
@@ -28673,7 +28669,7 @@
       <c r="C785" s="22" t="n">
         <v>4504</v>
       </c>
-      <c r="D785" s="33" t="s">
+      <c r="D785" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E785" s="22" t="n">
@@ -28702,7 +28698,7 @@
       <c r="C786" s="22" t="n">
         <v>4505</v>
       </c>
-      <c r="D786" s="33" t="s">
+      <c r="D786" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E786" s="22" t="n">
@@ -28731,7 +28727,7 @@
       <c r="C787" s="22" t="n">
         <v>4506</v>
       </c>
-      <c r="D787" s="33" t="s">
+      <c r="D787" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E787" s="22" t="s">
@@ -28760,7 +28756,7 @@
       <c r="C788" s="22" t="n">
         <v>4507</v>
       </c>
-      <c r="D788" s="33" t="s">
+      <c r="D788" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E788" s="22" t="s">
@@ -28789,7 +28785,7 @@
       <c r="C789" s="22" t="n">
         <v>4508</v>
       </c>
-      <c r="D789" s="33" t="s">
+      <c r="D789" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E789" s="22" t="s">
@@ -28818,7 +28814,7 @@
       <c r="C790" s="22" t="n">
         <v>4509</v>
       </c>
-      <c r="D790" s="33" t="s">
+      <c r="D790" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E790" s="22" t="n">
@@ -28844,7 +28840,7 @@
       <c r="C791" s="22" t="n">
         <v>4510</v>
       </c>
-      <c r="D791" s="33" t="s">
+      <c r="D791" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E791" s="22" t="n">
@@ -28873,7 +28869,7 @@
       <c r="C792" s="22" t="n">
         <v>4511</v>
       </c>
-      <c r="D792" s="33" t="s">
+      <c r="D792" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E792" s="22" t="n">
@@ -28902,7 +28898,7 @@
       <c r="C793" s="22" t="n">
         <v>4512</v>
       </c>
-      <c r="D793" s="33" t="s">
+      <c r="D793" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E793" s="22" t="n">
@@ -28931,7 +28927,7 @@
       <c r="C794" s="22" t="n">
         <v>4513</v>
       </c>
-      <c r="D794" s="33" t="s">
+      <c r="D794" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E794" s="22" t="n">
@@ -28960,7 +28956,7 @@
       <c r="C795" s="22" t="n">
         <v>4514</v>
       </c>
-      <c r="D795" s="33" t="s">
+      <c r="D795" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E795" s="22" t="n">
@@ -28989,7 +28985,7 @@
       <c r="C796" s="22" t="n">
         <v>4515</v>
       </c>
-      <c r="D796" s="33" t="s">
+      <c r="D796" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E796" s="22" t="n">
@@ -29018,7 +29014,7 @@
       <c r="C797" s="22" t="n">
         <v>4516</v>
       </c>
-      <c r="D797" s="33" t="s">
+      <c r="D797" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E797" s="22" t="s">
@@ -29047,7 +29043,7 @@
       <c r="C798" s="22" t="n">
         <v>4517</v>
       </c>
-      <c r="D798" s="33" t="s">
+      <c r="D798" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E798" s="22" t="s">
@@ -29076,7 +29072,7 @@
       <c r="C799" s="22" t="n">
         <v>4518</v>
       </c>
-      <c r="D799" s="33" t="s">
+      <c r="D799" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E799" s="22" t="s">
@@ -29105,7 +29101,7 @@
       <c r="C800" s="22" t="n">
         <v>4519</v>
       </c>
-      <c r="D800" s="33" t="s">
+      <c r="D800" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E800" s="22" t="n">
@@ -29134,7 +29130,7 @@
       <c r="C801" s="22" t="n">
         <v>4520</v>
       </c>
-      <c r="D801" s="33" t="s">
+      <c r="D801" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E801" s="22" t="n">
@@ -29163,7 +29159,7 @@
       <c r="C802" s="22" t="n">
         <v>4521</v>
       </c>
-      <c r="D802" s="33" t="s">
+      <c r="D802" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E802" s="22" t="n">
@@ -29192,7 +29188,7 @@
       <c r="C803" s="22" t="n">
         <v>4522</v>
       </c>
-      <c r="D803" s="33" t="s">
+      <c r="D803" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E803" s="22" t="n">
@@ -29221,7 +29217,7 @@
       <c r="C804" s="22" t="n">
         <v>4523</v>
       </c>
-      <c r="D804" s="33" t="s">
+      <c r="D804" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E804" s="22" t="n">
@@ -29250,7 +29246,7 @@
       <c r="C805" s="22" t="n">
         <v>4524</v>
       </c>
-      <c r="D805" s="33" t="s">
+      <c r="D805" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E805" s="22" t="n">
@@ -29279,7 +29275,7 @@
       <c r="C806" s="22" t="n">
         <v>4525</v>
       </c>
-      <c r="D806" s="33" t="s">
+      <c r="D806" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E806" s="22" t="n">
@@ -29308,7 +29304,7 @@
       <c r="C807" s="22" t="n">
         <v>4526</v>
       </c>
-      <c r="D807" s="33" t="s">
+      <c r="D807" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E807" s="22" t="n">
@@ -29337,7 +29333,7 @@
       <c r="C808" s="22" t="n">
         <v>4527</v>
       </c>
-      <c r="D808" s="33" t="s">
+      <c r="D808" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E808" s="22" t="n">
@@ -29366,7 +29362,7 @@
       <c r="C809" s="22" t="n">
         <v>4528</v>
       </c>
-      <c r="D809" s="33" t="s">
+      <c r="D809" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E809" s="22" t="n">
@@ -29395,7 +29391,7 @@
       <c r="C810" s="22" t="n">
         <v>4529</v>
       </c>
-      <c r="D810" s="33" t="s">
+      <c r="D810" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E810" s="22" t="n">
@@ -29424,7 +29420,7 @@
       <c r="C811" s="22" t="n">
         <v>4530</v>
       </c>
-      <c r="D811" s="33" t="s">
+      <c r="D811" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E811" s="22" t="n">
@@ -29453,7 +29449,7 @@
       <c r="C812" s="22" t="n">
         <v>4531</v>
       </c>
-      <c r="D812" s="33" t="s">
+      <c r="D812" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E812" s="22" t="n">
@@ -29482,7 +29478,7 @@
       <c r="C813" s="22" t="n">
         <v>4532</v>
       </c>
-      <c r="D813" s="33" t="s">
+      <c r="D813" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E813" s="22" t="n">
@@ -29511,7 +29507,7 @@
       <c r="C814" s="22" t="n">
         <v>4533</v>
       </c>
-      <c r="D814" s="33" t="s">
+      <c r="D814" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E814" s="22" t="n">
@@ -29540,7 +29536,7 @@
       <c r="C815" s="22" t="n">
         <v>4534</v>
       </c>
-      <c r="D815" s="33" t="s">
+      <c r="D815" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E815" s="22" t="n">
@@ -29569,7 +29565,7 @@
       <c r="C816" s="22" t="n">
         <v>4535</v>
       </c>
-      <c r="D816" s="33" t="s">
+      <c r="D816" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E816" s="22" t="n">
@@ -29598,7 +29594,7 @@
       <c r="C817" s="22" t="n">
         <v>4536</v>
       </c>
-      <c r="D817" s="33" t="s">
+      <c r="D817" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E817" s="22" t="n">
@@ -29627,7 +29623,7 @@
       <c r="C818" s="22" t="n">
         <v>4537</v>
       </c>
-      <c r="D818" s="33" t="s">
+      <c r="D818" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E818" s="22" t="n">
@@ -29656,7 +29652,7 @@
       <c r="C819" s="22" t="n">
         <v>4538</v>
       </c>
-      <c r="D819" s="33" t="s">
+      <c r="D819" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E819" s="22" t="n">
@@ -29685,7 +29681,7 @@
       <c r="C820" s="22" t="n">
         <v>4539</v>
       </c>
-      <c r="D820" s="33" t="s">
+      <c r="D820" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E820" s="22" t="n">
@@ -29714,7 +29710,7 @@
       <c r="C821" s="22" t="n">
         <v>4540</v>
       </c>
-      <c r="D821" s="33" t="s">
+      <c r="D821" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E821" s="22" t="n">
@@ -29743,7 +29739,7 @@
       <c r="C822" s="22" t="n">
         <v>4541</v>
       </c>
-      <c r="D822" s="33" t="s">
+      <c r="D822" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E822" s="22" t="n">
@@ -29772,7 +29768,7 @@
       <c r="C823" s="22" t="n">
         <v>4542</v>
       </c>
-      <c r="D823" s="33" t="s">
+      <c r="D823" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E823" s="22" t="n">
@@ -29801,7 +29797,7 @@
       <c r="C824" s="22" t="n">
         <v>4543</v>
       </c>
-      <c r="D824" s="33" t="s">
+      <c r="D824" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E824" s="22" t="n">
@@ -29830,7 +29826,7 @@
       <c r="C825" s="22" t="n">
         <v>4544</v>
       </c>
-      <c r="D825" s="33" t="s">
+      <c r="D825" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E825" s="22" t="n">
@@ -29859,7 +29855,7 @@
       <c r="C826" s="22" t="n">
         <v>4545</v>
       </c>
-      <c r="D826" s="33" t="s">
+      <c r="D826" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E826" s="22" t="n">
@@ -29888,7 +29884,7 @@
       <c r="C827" s="22" t="n">
         <v>4546</v>
       </c>
-      <c r="D827" s="33" t="s">
+      <c r="D827" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E827" s="22" t="n">
@@ -29917,7 +29913,7 @@
       <c r="C828" s="22" t="n">
         <v>4548</v>
       </c>
-      <c r="D828" s="33" t="s">
+      <c r="D828" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E828" s="22" t="n">
@@ -29946,7 +29942,7 @@
       <c r="C829" s="22" t="n">
         <v>4550</v>
       </c>
-      <c r="D829" s="33" t="s">
+      <c r="D829" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E829" s="22" t="n">
@@ -29975,7 +29971,7 @@
       <c r="C830" s="22" t="n">
         <v>4552</v>
       </c>
-      <c r="D830" s="33" t="s">
+      <c r="D830" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E830" s="22" t="n">
@@ -30004,7 +30000,7 @@
       <c r="C831" s="22" t="n">
         <v>4554</v>
       </c>
-      <c r="D831" s="33" t="s">
+      <c r="D831" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E831" s="22" t="n">
@@ -30033,7 +30029,7 @@
       <c r="C832" s="22" t="n">
         <v>4556</v>
       </c>
-      <c r="D832" s="33" t="s">
+      <c r="D832" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E832" s="22" t="n">
@@ -30062,7 +30058,7 @@
       <c r="C833" s="22" t="n">
         <v>4558</v>
       </c>
-      <c r="D833" s="33" t="s">
+      <c r="D833" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E833" s="22" t="n">
@@ -30091,7 +30087,7 @@
       <c r="C834" s="22" t="n">
         <v>4560</v>
       </c>
-      <c r="D834" s="33" t="s">
+      <c r="D834" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E834" s="22" t="n">
@@ -30120,7 +30116,7 @@
       <c r="C835" s="22" t="n">
         <v>4562</v>
       </c>
-      <c r="D835" s="33" t="s">
+      <c r="D835" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E835" s="22" t="n">
@@ -30149,7 +30145,7 @@
       <c r="C836" s="22" t="n">
         <v>4564</v>
       </c>
-      <c r="D836" s="33" t="s">
+      <c r="D836" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E836" s="22" t="n">
@@ -30178,7 +30174,7 @@
       <c r="C837" s="22" t="n">
         <v>4566</v>
       </c>
-      <c r="D837" s="33" t="s">
+      <c r="D837" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E837" s="22" t="n">
@@ -30207,7 +30203,7 @@
       <c r="C838" s="22" t="n">
         <v>4568</v>
       </c>
-      <c r="D838" s="33" t="s">
+      <c r="D838" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E838" s="22" t="n">
@@ -30236,7 +30232,7 @@
       <c r="C839" s="22" t="n">
         <v>4570</v>
       </c>
-      <c r="D839" s="33" t="s">
+      <c r="D839" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E839" s="22" t="n">
@@ -30265,7 +30261,7 @@
       <c r="C840" s="22" t="n">
         <v>4572</v>
       </c>
-      <c r="D840" s="33" t="s">
+      <c r="D840" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E840" s="22" t="n">
@@ -30294,7 +30290,7 @@
       <c r="C841" s="22" t="n">
         <v>4574</v>
       </c>
-      <c r="D841" s="33" t="s">
+      <c r="D841" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E841" s="22" t="n">
@@ -30323,7 +30319,7 @@
       <c r="C842" s="22" t="n">
         <v>4575</v>
       </c>
-      <c r="D842" s="33" t="s">
+      <c r="D842" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E842" s="22" t="n">
@@ -30352,7 +30348,7 @@
       <c r="C843" s="22" t="n">
         <v>4576</v>
       </c>
-      <c r="D843" s="33" t="s">
+      <c r="D843" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E843" s="22" t="n">
@@ -30381,7 +30377,7 @@
       <c r="C844" s="22" t="n">
         <v>4577</v>
       </c>
-      <c r="D844" s="33" t="s">
+      <c r="D844" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E844" s="1" t="n">
@@ -30410,7 +30406,7 @@
       <c r="C845" s="22" t="n">
         <v>4578</v>
       </c>
-      <c r="D845" s="33" t="s">
+      <c r="D845" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E845" s="22" t="n">
@@ -30443,7 +30439,7 @@
       <c r="C846" s="22" t="n">
         <v>4579</v>
       </c>
-      <c r="D846" s="33" t="s">
+      <c r="D846" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E846" s="22" t="n">
@@ -30476,7 +30472,7 @@
       <c r="C847" s="22" t="n">
         <v>4580</v>
       </c>
-      <c r="D847" s="33" t="s">
+      <c r="D847" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E847" s="22" t="n">
@@ -30509,7 +30505,7 @@
       <c r="C848" s="22" t="n">
         <v>4581</v>
       </c>
-      <c r="D848" s="33" t="s">
+      <c r="D848" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E848" s="22" t="n">
@@ -30542,7 +30538,7 @@
       <c r="C849" s="22" t="n">
         <v>4582</v>
       </c>
-      <c r="D849" s="33" t="s">
+      <c r="D849" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E849" s="22" t="n">
@@ -30575,7 +30571,7 @@
       <c r="C850" s="22" t="n">
         <v>4583</v>
       </c>
-      <c r="D850" s="33" t="s">
+      <c r="D850" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E850" s="22" t="n">
@@ -30608,7 +30604,7 @@
       <c r="C851" s="22" t="n">
         <v>4584</v>
       </c>
-      <c r="D851" s="33" t="s">
+      <c r="D851" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E851" s="22" t="n">
@@ -30641,7 +30637,7 @@
       <c r="C852" s="22" t="n">
         <v>4585</v>
       </c>
-      <c r="D852" s="33" t="s">
+      <c r="D852" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E852" s="22" t="n">
@@ -30674,7 +30670,7 @@
       <c r="C853" s="22" t="n">
         <v>4586</v>
       </c>
-      <c r="D853" s="33" t="s">
+      <c r="D853" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E853" s="22" t="n">
@@ -30707,7 +30703,7 @@
       <c r="C854" s="22" t="n">
         <v>4587</v>
       </c>
-      <c r="D854" s="33" t="s">
+      <c r="D854" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E854" s="22" t="n">
@@ -30740,7 +30736,7 @@
       <c r="C855" s="22" t="n">
         <v>4588</v>
       </c>
-      <c r="D855" s="33" t="s">
+      <c r="D855" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E855" s="22" t="n">
@@ -30773,7 +30769,7 @@
       <c r="C856" s="22" t="n">
         <v>4589</v>
       </c>
-      <c r="D856" s="33" t="s">
+      <c r="D856" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E856" s="22" t="n">
@@ -30806,7 +30802,7 @@
       <c r="C857" s="22" t="n">
         <v>4590</v>
       </c>
-      <c r="D857" s="33" t="s">
+      <c r="D857" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E857" s="22" t="n">
@@ -30839,7 +30835,7 @@
       <c r="C858" s="22" t="n">
         <v>4591</v>
       </c>
-      <c r="D858" s="33" t="s">
+      <c r="D858" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E858" s="22" t="n">
@@ -30872,7 +30868,7 @@
       <c r="C859" s="22" t="n">
         <v>4592</v>
       </c>
-      <c r="D859" s="33" t="s">
+      <c r="D859" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E859" s="22" t="n">
@@ -30905,7 +30901,7 @@
       <c r="C860" s="22" t="n">
         <v>4593</v>
       </c>
-      <c r="D860" s="33" t="s">
+      <c r="D860" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E860" s="22" t="n">
@@ -30938,7 +30934,7 @@
       <c r="C861" s="1" t="n">
         <v>4594</v>
       </c>
-      <c r="D861" s="33" t="s">
+      <c r="D861" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E861" s="1" t="n">
@@ -30967,7 +30963,7 @@
       <c r="C862" s="1" t="n">
         <v>4595</v>
       </c>
-      <c r="D862" s="33" t="s">
+      <c r="D862" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E862" s="1" t="n">
@@ -30996,7 +30992,7 @@
       <c r="C863" s="1" t="n">
         <v>4596</v>
       </c>
-      <c r="D863" s="33" t="s">
+      <c r="D863" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E863" s="1" t="n">
@@ -31025,7 +31021,7 @@
       <c r="C864" s="1" t="n">
         <v>4597</v>
       </c>
-      <c r="D864" s="33" t="s">
+      <c r="D864" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E864" s="1" t="n">
@@ -31054,7 +31050,7 @@
       <c r="C865" s="1" t="n">
         <v>4598</v>
       </c>
-      <c r="D865" s="33" t="s">
+      <c r="D865" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E865" s="1" t="n">
@@ -31083,7 +31079,7 @@
       <c r="C866" s="1" t="n">
         <v>4599</v>
       </c>
-      <c r="D866" s="33" t="s">
+      <c r="D866" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E866" s="1" t="n">
@@ -31112,7 +31108,7 @@
       <c r="C867" s="1" t="n">
         <v>4600</v>
       </c>
-      <c r="D867" s="33" t="s">
+      <c r="D867" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E867" s="1" t="n">
@@ -31141,7 +31137,7 @@
       <c r="C868" s="1" t="n">
         <v>4601</v>
       </c>
-      <c r="D868" s="33" t="s">
+      <c r="D868" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E868" s="1" t="n">
@@ -31170,7 +31166,7 @@
       <c r="C869" s="1" t="n">
         <v>4602</v>
       </c>
-      <c r="D869" s="33" t="s">
+      <c r="D869" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E869" s="1" t="n">
@@ -31231,7 +31227,7 @@
       <c r="C871" s="1" t="n">
         <v>4605</v>
       </c>
-      <c r="D871" s="33" t="s">
+      <c r="D871" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E871" s="1" t="n">
@@ -31260,7 +31256,7 @@
       <c r="C872" s="1" t="n">
         <v>4606</v>
       </c>
-      <c r="D872" s="33" t="s">
+      <c r="D872" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E872" s="1" t="n">
@@ -31289,7 +31285,7 @@
       <c r="C873" s="1" t="n">
         <v>4607</v>
       </c>
-      <c r="D873" s="33" t="s">
+      <c r="D873" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E873" s="1" t="n">
@@ -31318,7 +31314,7 @@
       <c r="C874" s="1" t="n">
         <v>4608</v>
       </c>
-      <c r="D874" s="33" t="s">
+      <c r="D874" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="1" t="n">
@@ -31347,7 +31343,7 @@
       <c r="C875" s="1" t="n">
         <v>4609</v>
       </c>
-      <c r="D875" s="33" t="s">
+      <c r="D875" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E875" s="1" t="n">
@@ -31376,7 +31372,7 @@
       <c r="C876" s="1" t="n">
         <v>4610</v>
       </c>
-      <c r="D876" s="33" t="s">
+      <c r="D876" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E876" s="1" t="n">
@@ -31405,7 +31401,7 @@
       <c r="C877" s="1" t="n">
         <v>4612</v>
       </c>
-      <c r="D877" s="33" t="s">
+      <c r="D877" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E877" s="1" t="n">
@@ -31434,7 +31430,7 @@
       <c r="C878" s="1" t="n">
         <v>4613</v>
       </c>
-      <c r="D878" s="33" t="s">
+      <c r="D878" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E878" s="1" t="n">
@@ -31463,7 +31459,7 @@
       <c r="C879" s="1" t="n">
         <v>4614</v>
       </c>
-      <c r="D879" s="33" t="s">
+      <c r="D879" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E879" s="1" t="n">
@@ -31492,7 +31488,7 @@
       <c r="C880" s="1" t="n">
         <v>4615</v>
       </c>
-      <c r="D880" s="33" t="s">
+      <c r="D880" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E880" s="1" t="n">
@@ -31521,7 +31517,7 @@
       <c r="C881" s="23" t="s">
         <v>1406</v>
       </c>
-      <c r="D881" s="33"/>
+      <c r="D881" s="32"/>
     </row>
     <row r="882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
@@ -31533,7 +31529,7 @@
       <c r="C882" s="1" t="n">
         <v>4620</v>
       </c>
-      <c r="D882" s="33" t="s">
+      <c r="D882" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E882" s="22" t="n">
@@ -31562,7 +31558,7 @@
       <c r="C883" s="1" t="n">
         <v>4621</v>
       </c>
-      <c r="D883" s="33"/>
+      <c r="D883" s="32"/>
       <c r="E883" s="22"/>
       <c r="G883" s="22" t="s">
         <v>117</v>
@@ -31580,7 +31576,7 @@
       <c r="C884" s="1" t="n">
         <v>4622</v>
       </c>
-      <c r="D884" s="33" t="s">
+      <c r="D884" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E884" s="22"/>
@@ -31718,7 +31714,7 @@
       <c r="C889" s="1" t="n">
         <v>4700</v>
       </c>
-      <c r="D889" s="33" t="s">
+      <c r="D889" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E889" s="1" t="n">
@@ -31747,7 +31743,7 @@
       <c r="C890" s="1" t="n">
         <v>4701</v>
       </c>
-      <c r="D890" s="33" t="s">
+      <c r="D890" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E890" s="1" t="n">
@@ -31776,7 +31772,7 @@
       <c r="C891" s="1" t="n">
         <v>4702</v>
       </c>
-      <c r="D891" s="33" t="s">
+      <c r="D891" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E891" s="1" t="n">
@@ -31805,7 +31801,7 @@
       <c r="C892" s="1" t="n">
         <v>4703</v>
       </c>
-      <c r="D892" s="33" t="s">
+      <c r="D892" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E892" s="1" t="n">
@@ -31834,7 +31830,7 @@
       <c r="C893" s="1" t="n">
         <v>4704</v>
       </c>
-      <c r="D893" s="33" t="s">
+      <c r="D893" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E893" s="1" t="n">
@@ -31863,7 +31859,7 @@
       <c r="C894" s="22" t="n">
         <v>4800</v>
       </c>
-      <c r="D894" s="33" t="s">
+      <c r="D894" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E894" s="22" t="n">
@@ -31889,7 +31885,7 @@
       <c r="C895" s="22" t="n">
         <v>4801</v>
       </c>
-      <c r="D895" s="33" t="s">
+      <c r="D895" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E895" s="22" t="n">
@@ -31915,7 +31911,7 @@
       <c r="C896" s="22" t="n">
         <v>4803</v>
       </c>
-      <c r="D896" s="33" t="s">
+      <c r="D896" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E896" s="22" t="n">
@@ -31944,7 +31940,7 @@
       <c r="C897" s="22" t="n">
         <v>4804</v>
       </c>
-      <c r="D897" s="33" t="s">
+      <c r="D897" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E897" s="22" t="n">
@@ -31973,7 +31969,7 @@
       <c r="C898" s="22" t="n">
         <v>4805</v>
       </c>
-      <c r="D898" s="33" t="s">
+      <c r="D898" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E898" s="22" t="n">
@@ -32002,7 +31998,7 @@
       <c r="C899" s="22" t="n">
         <v>4806</v>
       </c>
-      <c r="D899" s="33" t="s">
+      <c r="D899" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E899" s="22" t="n">
@@ -32031,7 +32027,7 @@
       <c r="C900" s="22" t="n">
         <v>4807</v>
       </c>
-      <c r="D900" s="33" t="s">
+      <c r="D900" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E900" s="22" t="n">
@@ -32060,7 +32056,7 @@
       <c r="C901" s="22" t="n">
         <v>4808</v>
       </c>
-      <c r="D901" s="33" t="s">
+      <c r="D901" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E901" s="22" t="n">
@@ -32089,7 +32085,7 @@
       <c r="C902" s="22" t="n">
         <v>4809</v>
       </c>
-      <c r="D902" s="33" t="s">
+      <c r="D902" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E902" s="22" t="n">
@@ -32118,7 +32114,7 @@
       <c r="C903" s="22" t="n">
         <v>4810</v>
       </c>
-      <c r="D903" s="33" t="s">
+      <c r="D903" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E903" s="22" t="n">
@@ -32147,7 +32143,7 @@
       <c r="C904" s="22" t="n">
         <v>4811</v>
       </c>
-      <c r="D904" s="33" t="s">
+      <c r="D904" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E904" s="22" t="n">
@@ -32176,7 +32172,7 @@
       <c r="C905" s="24" t="s">
         <v>1423</v>
       </c>
-      <c r="D905" s="33"/>
+      <c r="D905" s="32"/>
       <c r="E905" s="22"/>
       <c r="G905" s="22" t="s">
         <v>117</v>
@@ -32193,7 +32189,7 @@
       <c r="C906" s="22" t="n">
         <v>4820</v>
       </c>
-      <c r="D906" s="33" t="s">
+      <c r="D906" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E906" s="22"/>
@@ -32215,7 +32211,7 @@
       <c r="C907" s="22" t="n">
         <v>4900</v>
       </c>
-      <c r="D907" s="33" t="s">
+      <c r="D907" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E907" s="22" t="n">
@@ -32244,7 +32240,7 @@
       <c r="C908" s="22" t="n">
         <v>4901</v>
       </c>
-      <c r="D908" s="33" t="s">
+      <c r="D908" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E908" s="22" t="n">
@@ -32273,7 +32269,7 @@
       <c r="C909" s="22" t="n">
         <v>4902</v>
       </c>
-      <c r="D909" s="33" t="s">
+      <c r="D909" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E909" s="22" t="n">
@@ -32302,7 +32298,7 @@
       <c r="C910" s="22" t="n">
         <v>4903</v>
       </c>
-      <c r="D910" s="33" t="s">
+      <c r="D910" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E910" s="22" t="n">
@@ -32331,7 +32327,7 @@
       <c r="C911" s="22" t="n">
         <v>4904</v>
       </c>
-      <c r="D911" s="33" t="s">
+      <c r="D911" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E911" s="22" t="n">
@@ -32360,7 +32356,7 @@
       <c r="C912" s="22" t="n">
         <v>4905</v>
       </c>
-      <c r="D912" s="33" t="s">
+      <c r="D912" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E912" s="22" t="n">
@@ -32389,7 +32385,7 @@
       <c r="C913" s="22" t="n">
         <v>4906</v>
       </c>
-      <c r="D913" s="33" t="s">
+      <c r="D913" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E913" s="22" t="n">
@@ -32418,7 +32414,7 @@
       <c r="C914" s="22" t="n">
         <v>4907</v>
       </c>
-      <c r="D914" s="33" t="s">
+      <c r="D914" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E914" s="22" t="s">
@@ -32447,7 +32443,7 @@
       <c r="C915" s="22" t="n">
         <v>4908</v>
       </c>
-      <c r="D915" s="33" t="s">
+      <c r="D915" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E915" s="22" t="s">
@@ -32476,7 +32472,7 @@
       <c r="C916" s="22" t="n">
         <v>4909</v>
       </c>
-      <c r="D916" s="33" t="s">
+      <c r="D916" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E916" s="22" t="s">
@@ -32505,7 +32501,7 @@
       <c r="C917" s="22" t="n">
         <v>4910</v>
       </c>
-      <c r="D917" s="33" t="s">
+      <c r="D917" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E917" s="22" t="n">
@@ -32534,7 +32530,7 @@
       <c r="C918" s="22" t="n">
         <v>4911</v>
       </c>
-      <c r="D918" s="33" t="s">
+      <c r="D918" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E918" s="22" t="n">
@@ -32563,7 +32559,7 @@
       <c r="C919" s="22" t="n">
         <v>4912</v>
       </c>
-      <c r="D919" s="33" t="s">
+      <c r="D919" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E919" s="22" t="n">
@@ -32592,7 +32588,7 @@
       <c r="C920" s="22" t="n">
         <v>4913</v>
       </c>
-      <c r="D920" s="33" t="s">
+      <c r="D920" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E920" s="22" t="n">
@@ -32621,7 +32617,7 @@
       <c r="C921" s="22" t="n">
         <v>4914</v>
       </c>
-      <c r="D921" s="33" t="s">
+      <c r="D921" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E921" s="22" t="n">
@@ -32650,7 +32646,7 @@
       <c r="C922" s="22" t="n">
         <v>4915</v>
       </c>
-      <c r="D922" s="33" t="s">
+      <c r="D922" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E922" s="22" t="n">
@@ -32679,7 +32675,7 @@
       <c r="C923" s="22" t="n">
         <v>4916</v>
       </c>
-      <c r="D923" s="33" t="s">
+      <c r="D923" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E923" s="22" t="n">
@@ -32708,7 +32704,7 @@
       <c r="C924" s="22" t="n">
         <v>4917</v>
       </c>
-      <c r="D924" s="33" t="s">
+      <c r="D924" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E924" s="22" t="s">
@@ -32737,7 +32733,7 @@
       <c r="C925" s="22" t="n">
         <v>4918</v>
       </c>
-      <c r="D925" s="33" t="s">
+      <c r="D925" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E925" s="22" t="s">
@@ -32766,7 +32762,7 @@
       <c r="C926" s="22" t="n">
         <v>4919</v>
       </c>
-      <c r="D926" s="33" t="s">
+      <c r="D926" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E926" s="22" t="s">
@@ -32795,7 +32791,7 @@
       <c r="C927" s="22" t="n">
         <v>4920</v>
       </c>
-      <c r="D927" s="33" t="s">
+      <c r="D927" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E927" s="22" t="n">
@@ -32824,7 +32820,7 @@
       <c r="C928" s="22" t="n">
         <v>4921</v>
       </c>
-      <c r="D928" s="33" t="s">
+      <c r="D928" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E928" s="22" t="n">
@@ -32853,7 +32849,7 @@
       <c r="C929" s="22" t="n">
         <v>4922</v>
       </c>
-      <c r="D929" s="33" t="s">
+      <c r="D929" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E929" s="22" t="n">
@@ -32882,7 +32878,7 @@
       <c r="C930" s="22" t="n">
         <v>4924</v>
       </c>
-      <c r="D930" s="33" t="s">
+      <c r="D930" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E930" s="22" t="n">
@@ -32911,7 +32907,7 @@
       <c r="C931" s="1" t="n">
         <v>4925</v>
       </c>
-      <c r="D931" s="33" t="s">
+      <c r="D931" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E931" s="1" t="n">
@@ -33176,7 +33172,7 @@
       <c r="C942" s="25" t="n">
         <v>5200</v>
       </c>
-      <c r="D942" s="33" t="s">
+      <c r="D942" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E942" s="25" t="n">
@@ -33202,7 +33198,7 @@
       <c r="C943" s="25" t="n">
         <v>5201</v>
       </c>
-      <c r="D943" s="33" t="s">
+      <c r="D943" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E943" s="25" t="n">
@@ -33228,7 +33224,7 @@
       <c r="C944" s="25" t="n">
         <v>5202</v>
       </c>
-      <c r="D944" s="33" t="s">
+      <c r="D944" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E944" s="25" t="n">
@@ -33254,7 +33250,7 @@
       <c r="C945" s="25" t="n">
         <v>5203</v>
       </c>
-      <c r="D945" s="33" t="s">
+      <c r="D945" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E945" s="25" t="n">
@@ -33280,7 +33276,7 @@
       <c r="C946" s="25" t="n">
         <v>5204</v>
       </c>
-      <c r="D946" s="33" t="s">
+      <c r="D946" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E946" s="25" t="n">
@@ -33309,7 +33305,7 @@
       <c r="C947" s="25" t="n">
         <v>5205</v>
       </c>
-      <c r="D947" s="33" t="s">
+      <c r="D947" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E947" s="25" t="n">
@@ -33338,7 +33334,7 @@
       <c r="C948" s="25" t="n">
         <v>5206</v>
       </c>
-      <c r="D948" s="33" t="s">
+      <c r="D948" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E948" s="25" t="n">
@@ -33367,7 +33363,7 @@
       <c r="C949" s="25" t="n">
         <v>5207</v>
       </c>
-      <c r="D949" s="33" t="s">
+      <c r="D949" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E949" s="25" t="n">
@@ -33396,7 +33392,7 @@
       <c r="C950" s="25" t="n">
         <v>5208</v>
       </c>
-      <c r="D950" s="33" t="s">
+      <c r="D950" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E950" s="25" t="n">
@@ -33425,7 +33421,7 @@
       <c r="C951" s="25" t="n">
         <v>5209</v>
       </c>
-      <c r="D951" s="33" t="s">
+      <c r="D951" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E951" s="25" t="s">
@@ -33454,7 +33450,7 @@
       <c r="C952" s="25" t="n">
         <v>5210</v>
       </c>
-      <c r="D952" s="33" t="s">
+      <c r="D952" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E952" s="25" t="n">
@@ -33483,7 +33479,7 @@
       <c r="C953" s="25" t="n">
         <v>5211</v>
       </c>
-      <c r="D953" s="33" t="s">
+      <c r="D953" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E953" s="25" t="n">
@@ -33512,7 +33508,7 @@
       <c r="C954" s="25" t="n">
         <v>5212</v>
       </c>
-      <c r="D954" s="33" t="s">
+      <c r="D954" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E954" s="25" t="n">
@@ -33541,7 +33537,7 @@
       <c r="C955" s="25" t="n">
         <v>5213</v>
       </c>
-      <c r="D955" s="33" t="s">
+      <c r="D955" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E955" s="25" t="n">
@@ -33570,7 +33566,7 @@
       <c r="C956" s="25" t="n">
         <v>5214</v>
       </c>
-      <c r="D956" s="33" t="s">
+      <c r="D956" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E956" s="25" t="n">
@@ -33599,7 +33595,7 @@
       <c r="C957" s="25" t="n">
         <v>5215</v>
       </c>
-      <c r="D957" s="33" t="s">
+      <c r="D957" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E957" s="25" t="n">
@@ -33628,7 +33624,7 @@
       <c r="C958" s="25" t="n">
         <v>5216</v>
       </c>
-      <c r="D958" s="33" t="s">
+      <c r="D958" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E958" s="25" t="n">
@@ -33657,7 +33653,7 @@
       <c r="C959" s="25" t="n">
         <v>5217</v>
       </c>
-      <c r="D959" s="33" t="s">
+      <c r="D959" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E959" s="25" t="n">
@@ -33680,7 +33676,7 @@
       <c r="C960" s="25" t="n">
         <v>5218</v>
       </c>
-      <c r="D960" s="33" t="s">
+      <c r="D960" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E960" s="25" t="n">
@@ -33706,7 +33702,7 @@
       <c r="C961" s="25" t="n">
         <v>5234</v>
       </c>
-      <c r="D961" s="33" t="s">
+      <c r="D961" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E961" s="25" t="n">
@@ -33729,7 +33725,7 @@
       <c r="C962" s="25" t="n">
         <v>5250</v>
       </c>
-      <c r="D962" s="33" t="s">
+      <c r="D962" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E962" s="25" t="n">
@@ -33752,7 +33748,7 @@
       <c r="C963" s="25" t="n">
         <v>5266</v>
       </c>
-      <c r="D963" s="33" t="s">
+      <c r="D963" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E963" s="25" t="n">
@@ -33775,7 +33771,7 @@
       <c r="C964" s="25" t="n">
         <v>5282</v>
       </c>
-      <c r="D964" s="33" t="s">
+      <c r="D964" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E964" s="25" t="n">
@@ -33798,7 +33794,7 @@
       <c r="C965" s="25" t="n">
         <v>5298</v>
       </c>
-      <c r="D965" s="33" t="s">
+      <c r="D965" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E965" s="25" t="n">
@@ -33821,7 +33817,7 @@
       <c r="C966" s="25" t="n">
         <v>5314</v>
       </c>
-      <c r="D966" s="33" t="s">
+      <c r="D966" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E966" s="25" t="n">
@@ -33844,7 +33840,7 @@
       <c r="C967" s="25" t="n">
         <v>5330</v>
       </c>
-      <c r="D967" s="33" t="s">
+      <c r="D967" s="32" t="s">
         <v>1165</v>
       </c>
       <c r="E967" s="25" t="n">
@@ -33867,7 +33863,7 @@
       <c r="C968" s="24" t="s">
         <v>1449</v>
       </c>
-      <c r="D968" s="33"/>
+      <c r="D968" s="32"/>
       <c r="E968" s="25"/>
       <c r="G968" s="25" t="s">
         <v>117</v>
@@ -33883,7 +33879,7 @@
       <c r="C969" s="25" t="n">
         <v>5350</v>
       </c>
-      <c r="D969" s="33" t="s">
+      <c r="D969" s="32" t="s">
         <v>437</v>
       </c>
       <c r="E969" s="25"/>
@@ -33904,7 +33900,7 @@
       <c r="C970" s="1" t="n">
         <v>5400</v>
       </c>
-      <c r="D970" s="33" t="s">
+      <c r="D970" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E970" s="1" t="n">
@@ -33933,7 +33929,7 @@
       <c r="C971" s="1" t="n">
         <v>5401</v>
       </c>
-      <c r="D971" s="33" t="s">
+      <c r="D971" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E971" s="1" t="n">
@@ -33962,7 +33958,7 @@
       <c r="C972" s="1" t="n">
         <v>5402</v>
       </c>
-      <c r="D972" s="33" t="s">
+      <c r="D972" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E972" s="1" t="n">
@@ -33985,13 +33981,13 @@
       <c r="A973" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B973" s="29" t="s">
+      <c r="B973" s="28" t="s">
         <v>1459</v>
       </c>
       <c r="C973" s="1" t="n">
         <v>5403</v>
       </c>
-      <c r="D973" s="33" t="s">
+      <c r="D973" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E973" s="1" t="n">
@@ -34017,7 +34013,7 @@
       <c r="C974" s="1" t="n">
         <v>5404</v>
       </c>
-      <c r="D974" s="33" t="s">
+      <c r="D974" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E974" s="1" t="n">
@@ -34046,7 +34042,7 @@
       <c r="C975" s="1" t="n">
         <v>5405</v>
       </c>
-      <c r="D975" s="33" t="s">
+      <c r="D975" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E975" s="1" t="n">
@@ -34075,7 +34071,7 @@
       <c r="C976" s="1" t="n">
         <v>5406</v>
       </c>
-      <c r="D976" s="33" t="s">
+      <c r="D976" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E976" s="1" t="n">
@@ -34104,7 +34100,7 @@
       <c r="C977" s="1" t="n">
         <v>5407</v>
       </c>
-      <c r="D977" s="33" t="s">
+      <c r="D977" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E977" s="1" t="n">
@@ -34133,7 +34129,7 @@
       <c r="C978" s="1" t="n">
         <v>5420</v>
       </c>
-      <c r="D978" s="33" t="s">
+      <c r="D978" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E978" s="1" t="n">
@@ -34162,7 +34158,7 @@
       <c r="C979" s="1" t="n">
         <v>5421</v>
       </c>
-      <c r="D979" s="33" t="s">
+      <c r="D979" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E979" s="1" t="n">
@@ -34191,7 +34187,7 @@
       <c r="C980" s="1" t="n">
         <v>5422</v>
       </c>
-      <c r="D980" s="33" t="s">
+      <c r="D980" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E980" s="1" t="n">
@@ -34220,7 +34216,7 @@
       <c r="C981" s="1" t="n">
         <v>5423</v>
       </c>
-      <c r="D981" s="33" t="s">
+      <c r="D981" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E981" s="1" t="n">
@@ -34249,7 +34245,7 @@
       <c r="C982" s="1" t="n">
         <v>5424</v>
       </c>
-      <c r="D982" s="33" t="s">
+      <c r="D982" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E982" s="1" t="n">
@@ -34278,7 +34274,7 @@
       <c r="C983" s="1" t="n">
         <v>5425</v>
       </c>
-      <c r="D983" s="33" t="s">
+      <c r="D983" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E983" s="1" t="n">
@@ -34307,7 +34303,7 @@
       <c r="C984" s="1" t="n">
         <v>5426</v>
       </c>
-      <c r="D984" s="33" t="s">
+      <c r="D984" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E984" s="1" t="n">
@@ -34336,7 +34332,7 @@
       <c r="C985" s="1" t="n">
         <v>5427</v>
       </c>
-      <c r="D985" s="33" t="s">
+      <c r="D985" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E985" s="1" t="n">
@@ -34391,7 +34387,7 @@
       <c r="C987" s="1" t="n">
         <v>5430</v>
       </c>
-      <c r="D987" s="33" t="s">
+      <c r="D987" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E987" s="1" t="n">
@@ -34871,58 +34867,58 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>1521</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="34" t="s">
         <v>1522</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>1523</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>1524</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="35" t="s">
         <v>1525</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="35" t="s">
         <v>1526</v>
       </c>
     </row>
@@ -35090,24 +35086,24 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="n">
+      <c r="A28" s="34" t="n">
         <v>223</v>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="34" t="n">
         <v>277</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>1528</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="n">
+      <c r="A29" s="34" t="n">
         <v>224</v>
       </c>
-      <c r="B29" s="35" t="n">
+      <c r="B29" s="34" t="n">
         <v>278</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="34" t="s">
         <v>1529</v>
       </c>
     </row>
@@ -35123,57 +35119,57 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35" t="n">
+      <c r="A31" s="34" t="n">
         <v>226</v>
       </c>
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="34" t="n">
         <v>279</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="34" t="s">
         <v>1531</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35" t="n">
+      <c r="A32" s="34" t="n">
         <v>227</v>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="34" t="n">
         <v>276</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="34" t="s">
         <v>1532</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35" t="n">
+      <c r="A33" s="34" t="n">
         <v>228</v>
       </c>
-      <c r="B33" s="35" t="n">
+      <c r="B33" s="34" t="n">
         <v>275</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="34" t="s">
         <v>1533</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35" t="n">
+      <c r="A34" s="34" t="n">
         <v>229</v>
       </c>
-      <c r="B34" s="35" t="n">
+      <c r="B34" s="34" t="n">
         <v>274</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="34" t="s">
         <v>1534</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35" t="n">
+      <c r="A35" s="34" t="n">
         <v>230</v>
       </c>
-      <c r="B35" s="35" t="n">
+      <c r="B35" s="34" t="n">
         <v>273</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="34" t="s">
         <v>1535</v>
       </c>
     </row>
@@ -35277,35 +35273,35 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="35" t="n">
+      <c r="A45" s="34" t="n">
         <v>242</v>
       </c>
-      <c r="B45" s="35" t="n">
+      <c r="B45" s="34" t="n">
         <v>261</v>
       </c>
-      <c r="C45" s="35" t="s">
+      <c r="C45" s="34" t="s">
         <v>1545</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="35" t="n">
+      <c r="A46" s="34" t="n">
         <v>243</v>
       </c>
-      <c r="B46" s="35" t="n">
+      <c r="B46" s="34" t="n">
         <v>260</v>
       </c>
-      <c r="C46" s="35" t="s">
+      <c r="C46" s="34" t="s">
         <v>1546</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="35" t="n">
+      <c r="A47" s="34" t="n">
         <v>244</v>
       </c>
-      <c r="B47" s="35" t="n">
+      <c r="B47" s="34" t="n">
         <v>259</v>
       </c>
-      <c r="C47" s="35"/>
+      <c r="C47" s="34"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="n">
@@ -35314,7 +35310,7 @@
       <c r="B48" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="C48" s="35" t="s">
+      <c r="C48" s="34" t="s">
         <v>1547</v>
       </c>
     </row>
@@ -35371,7 +35367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.57"/>
@@ -35604,7 +35600,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="36" t="s">
         <v>1599</v>
       </c>
     </row>
@@ -36395,30 +36391,32 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="22" t="s">
+      <c r="A172" s="0"/>
+      <c r="B172" s="22" t="s">
         <v>1773</v>
-      </c>
-      <c r="B172" s="22" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B173" s="22" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B174" s="22" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="22" t="s">
         <v>1776</v>
       </c>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B175" s="22" t="s">
         <v>1777</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="22" t="s">
+      <c r="A176" s="0"/>
+      <c r="B176" s="25" t="s">
         <v>1778</v>
       </c>
     </row>
@@ -36433,7 +36431,7 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="25" t="s">
+      <c r="B179" s="22" t="s">
         <v>1781</v>
       </c>
     </row>
@@ -36452,6 +36450,8 @@
         <v>1784</v>
       </c>
     </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Field list" sheetId="1" state="visible" r:id="rId3"/>
@@ -5677,7 +5677,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5735,13 +5735,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Liberation Mono;Courier New;DejaVu Sans Mono;Monaco"/>
-      <family val="3"/>
       <charset val="1"/>
     </font>
     <font>
@@ -5860,7 +5853,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5978,10 +5971,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5993,7 +5982,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -24396,7 +24385,7 @@
       <c r="F627" s="3" t="s">
         <v>1215</v>
       </c>
-      <c r="G627" s="29" t="s">
+      <c r="G627" s="1" t="s">
         <v>1216</v>
       </c>
       <c r="H627" s="1" t="s">
@@ -25764,7 +25753,7 @@
       <c r="E678" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F678" s="30" t="s">
+      <c r="F678" s="29" t="s">
         <v>750</v>
       </c>
       <c r="G678" s="1" t="s">
@@ -25822,7 +25811,7 @@
       <c r="E680" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F680" s="31" t="s">
+      <c r="F680" s="30" t="s">
         <v>1307</v>
       </c>
       <c r="G680" s="1" t="s">
@@ -25848,7 +25837,7 @@
       <c r="E681" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F681" s="31" t="s">
+      <c r="F681" s="30" t="s">
         <v>1307</v>
       </c>
       <c r="G681" s="1" t="s">
@@ -26339,13 +26328,13 @@
       <c r="C700" s="1" t="n">
         <v>3924</v>
       </c>
-      <c r="D700" s="32" t="s">
+      <c r="D700" s="31" t="s">
         <v>136</v>
       </c>
       <c r="E700" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F700" s="31" t="s">
+      <c r="F700" s="30" t="s">
         <v>140</v>
       </c>
       <c r="G700" s="1" t="s">
@@ -26368,13 +26357,13 @@
       <c r="C701" s="1" t="n">
         <v>3926</v>
       </c>
-      <c r="D701" s="32" t="s">
+      <c r="D701" s="31" t="s">
         <v>136</v>
       </c>
       <c r="E701" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F701" s="31" t="s">
+      <c r="F701" s="30" t="s">
         <v>140</v>
       </c>
       <c r="G701" s="1" t="s">
@@ -26397,13 +26386,13 @@
       <c r="C702" s="1" t="n">
         <v>3928</v>
       </c>
-      <c r="D702" s="32" t="s">
+      <c r="D702" s="31" t="s">
         <v>136</v>
       </c>
       <c r="E702" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F702" s="31" t="s">
+      <c r="F702" s="30" t="s">
         <v>140</v>
       </c>
       <c r="G702" s="1" t="s">
@@ -26564,7 +26553,7 @@
       <c r="C709" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="D709" s="32" t="s">
+      <c r="D709" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E709" s="22" t="n">
@@ -26593,7 +26582,7 @@
       <c r="C710" s="22" t="n">
         <v>4001</v>
       </c>
-      <c r="D710" s="32" t="s">
+      <c r="D710" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E710" s="22" t="n">
@@ -26622,7 +26611,7 @@
       <c r="C711" s="22" t="n">
         <v>4002</v>
       </c>
-      <c r="D711" s="32" t="s">
+      <c r="D711" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E711" s="22" t="n">
@@ -26651,7 +26640,7 @@
       <c r="C712" s="22" t="n">
         <v>4003</v>
       </c>
-      <c r="D712" s="32" t="s">
+      <c r="D712" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E712" s="22" t="n">
@@ -26680,7 +26669,7 @@
       <c r="C713" s="22" t="n">
         <v>4004</v>
       </c>
-      <c r="D713" s="32" t="s">
+      <c r="D713" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E713" s="22" t="n">
@@ -26709,7 +26698,7 @@
       <c r="C714" s="22" t="n">
         <v>4006</v>
       </c>
-      <c r="D714" s="32" t="s">
+      <c r="D714" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E714" s="22" t="n">
@@ -26738,7 +26727,7 @@
       <c r="C715" s="22" t="n">
         <v>4007</v>
       </c>
-      <c r="D715" s="32" t="s">
+      <c r="D715" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E715" s="22" t="n">
@@ -26767,7 +26756,7 @@
       <c r="C716" s="22" t="n">
         <v>4008</v>
       </c>
-      <c r="D716" s="32" t="s">
+      <c r="D716" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E716" s="22" t="n">
@@ -26796,7 +26785,7 @@
       <c r="C717" s="22" t="n">
         <v>4009</v>
       </c>
-      <c r="D717" s="32" t="s">
+      <c r="D717" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E717" s="22" t="n">
@@ -26825,7 +26814,7 @@
       <c r="C718" s="22" t="n">
         <v>4010</v>
       </c>
-      <c r="D718" s="32" t="s">
+      <c r="D718" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E718" s="22" t="n">
@@ -26854,7 +26843,7 @@
       <c r="C719" s="22" t="n">
         <v>4011</v>
       </c>
-      <c r="D719" s="32" t="s">
+      <c r="D719" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E719" s="22" t="n">
@@ -26883,7 +26872,7 @@
       <c r="C720" s="22" t="n">
         <v>4100</v>
       </c>
-      <c r="D720" s="32" t="s">
+      <c r="D720" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E720" s="22" t="n">
@@ -26912,7 +26901,7 @@
       <c r="C721" s="22" t="n">
         <v>4101</v>
       </c>
-      <c r="D721" s="32" t="s">
+      <c r="D721" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E721" s="22" t="n">
@@ -26941,7 +26930,7 @@
       <c r="C722" s="22" t="n">
         <v>4102</v>
       </c>
-      <c r="D722" s="32" t="s">
+      <c r="D722" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E722" s="22" t="n">
@@ -26970,7 +26959,7 @@
       <c r="C723" s="22" t="n">
         <v>4103</v>
       </c>
-      <c r="D723" s="32" t="s">
+      <c r="D723" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E723" s="22" t="n">
@@ -26999,7 +26988,7 @@
       <c r="C724" s="22" t="n">
         <v>4104</v>
       </c>
-      <c r="D724" s="32" t="s">
+      <c r="D724" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E724" s="22" t="n">
@@ -27028,7 +27017,7 @@
       <c r="C725" s="22" t="n">
         <v>4106</v>
       </c>
-      <c r="D725" s="32" t="s">
+      <c r="D725" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E725" s="22" t="n">
@@ -27057,7 +27046,7 @@
       <c r="C726" s="22" t="n">
         <v>4107</v>
       </c>
-      <c r="D726" s="32" t="s">
+      <c r="D726" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E726" s="22" t="n">
@@ -27086,7 +27075,7 @@
       <c r="C727" s="22" t="n">
         <v>4108</v>
       </c>
-      <c r="D727" s="32" t="s">
+      <c r="D727" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E727" s="22" t="n">
@@ -27115,7 +27104,7 @@
       <c r="C728" s="22" t="n">
         <v>4109</v>
       </c>
-      <c r="D728" s="32" t="s">
+      <c r="D728" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E728" s="22" t="n">
@@ -27144,7 +27133,7 @@
       <c r="C729" s="22" t="n">
         <v>4110</v>
       </c>
-      <c r="D729" s="32" t="s">
+      <c r="D729" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E729" s="22" t="n">
@@ -27173,7 +27162,7 @@
       <c r="C730" s="22" t="n">
         <v>4111</v>
       </c>
-      <c r="D730" s="32" t="s">
+      <c r="D730" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E730" s="22" t="n">
@@ -27202,7 +27191,7 @@
       <c r="C731" s="22" t="n">
         <v>4112</v>
       </c>
-      <c r="D731" s="32" t="s">
+      <c r="D731" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E731" s="22" t="n">
@@ -27231,7 +27220,7 @@
       <c r="C732" s="22" t="n">
         <v>4113</v>
       </c>
-      <c r="D732" s="32" t="s">
+      <c r="D732" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E732" s="22" t="n">
@@ -27260,7 +27249,7 @@
       <c r="C733" s="22" t="n">
         <v>4114</v>
       </c>
-      <c r="D733" s="32" t="s">
+      <c r="D733" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E733" s="22" t="n">
@@ -27289,7 +27278,7 @@
       <c r="C734" s="22" t="n">
         <v>4115</v>
       </c>
-      <c r="D734" s="32" t="s">
+      <c r="D734" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E734" s="22" t="n">
@@ -27318,7 +27307,7 @@
       <c r="C735" s="22" t="n">
         <v>4116</v>
       </c>
-      <c r="D735" s="32" t="s">
+      <c r="D735" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E735" s="22" t="n">
@@ -27347,7 +27336,7 @@
       <c r="C736" s="22" t="n">
         <v>4117</v>
       </c>
-      <c r="D736" s="32" t="s">
+      <c r="D736" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E736" s="22" t="n">
@@ -27376,7 +27365,7 @@
       <c r="C737" s="22" t="n">
         <v>4118</v>
       </c>
-      <c r="D737" s="32" t="s">
+      <c r="D737" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E737" s="22" t="n">
@@ -27405,7 +27394,7 @@
       <c r="C738" s="22" t="n">
         <v>4119</v>
       </c>
-      <c r="D738" s="32" t="s">
+      <c r="D738" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E738" s="22" t="n">
@@ -27434,7 +27423,7 @@
       <c r="C739" s="22" t="n">
         <v>4120</v>
       </c>
-      <c r="D739" s="32" t="s">
+      <c r="D739" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E739" s="22" t="n">
@@ -27463,7 +27452,7 @@
       <c r="C740" s="22" t="s">
         <v>1338</v>
       </c>
-      <c r="D740" s="32"/>
+      <c r="D740" s="31"/>
       <c r="E740" s="22"/>
       <c r="G740" s="22" t="s">
         <v>117</v>
@@ -27479,7 +27468,7 @@
       <c r="C741" s="22" t="n">
         <v>4220</v>
       </c>
-      <c r="D741" s="32" t="s">
+      <c r="D741" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E741" s="22"/>
@@ -27500,7 +27489,7 @@
       <c r="C742" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="D742" s="32" t="s">
+      <c r="D742" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E742" s="22" t="n">
@@ -27529,7 +27518,7 @@
       <c r="C743" s="22" t="n">
         <v>4201</v>
       </c>
-      <c r="D743" s="32" t="s">
+      <c r="D743" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E743" s="22" t="n">
@@ -27558,7 +27547,7 @@
       <c r="C744" s="22" t="n">
         <v>4202</v>
       </c>
-      <c r="D744" s="32" t="s">
+      <c r="D744" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E744" s="22" t="n">
@@ -27587,7 +27576,7 @@
       <c r="C745" s="22" t="n">
         <v>4203</v>
       </c>
-      <c r="D745" s="32" t="s">
+      <c r="D745" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E745" s="22" t="n">
@@ -27616,7 +27605,7 @@
       <c r="C746" s="22" t="n">
         <v>4204</v>
       </c>
-      <c r="D746" s="32" t="s">
+      <c r="D746" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E746" s="22" t="n">
@@ -27645,7 +27634,7 @@
       <c r="C747" s="22" t="n">
         <v>4206</v>
       </c>
-      <c r="D747" s="32" t="s">
+      <c r="D747" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E747" s="22" t="n">
@@ -27674,7 +27663,7 @@
       <c r="C748" s="22" t="n">
         <v>4207</v>
       </c>
-      <c r="D748" s="32" t="s">
+      <c r="D748" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E748" s="22" t="n">
@@ -27703,7 +27692,7 @@
       <c r="C749" s="22" t="n">
         <v>4208</v>
       </c>
-      <c r="D749" s="32" t="s">
+      <c r="D749" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E749" s="22" t="n">
@@ -27732,7 +27721,7 @@
       <c r="C750" s="22" t="n">
         <v>4209</v>
       </c>
-      <c r="D750" s="32" t="s">
+      <c r="D750" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E750" s="22" t="n">
@@ -27761,7 +27750,7 @@
       <c r="C751" s="22" t="n">
         <v>4210</v>
       </c>
-      <c r="D751" s="32" t="s">
+      <c r="D751" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E751" s="22" t="n">
@@ -27790,7 +27779,7 @@
       <c r="C752" s="22" t="n">
         <v>4211</v>
       </c>
-      <c r="D752" s="32" t="s">
+      <c r="D752" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E752" s="22" t="n">
@@ -27819,7 +27808,7 @@
       <c r="C753" s="24" t="s">
         <v>1340</v>
       </c>
-      <c r="D753" s="32"/>
+      <c r="D753" s="31"/>
       <c r="E753" s="22"/>
       <c r="G753" s="22" t="s">
         <v>117</v>
@@ -27835,7 +27824,7 @@
       <c r="C754" s="22" t="n">
         <v>4220</v>
       </c>
-      <c r="D754" s="32" t="s">
+      <c r="D754" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E754" s="22"/>
@@ -27856,7 +27845,7 @@
       <c r="C755" s="22" t="n">
         <v>4300</v>
       </c>
-      <c r="D755" s="32" t="s">
+      <c r="D755" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E755" s="22" t="n">
@@ -27885,7 +27874,7 @@
       <c r="C756" s="22" t="n">
         <v>4301</v>
       </c>
-      <c r="D756" s="32" t="s">
+      <c r="D756" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E756" s="22" t="n">
@@ -27914,7 +27903,7 @@
       <c r="C757" s="22" t="n">
         <v>4302</v>
       </c>
-      <c r="D757" s="32" t="s">
+      <c r="D757" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E757" s="22" t="n">
@@ -27943,7 +27932,7 @@
       <c r="C758" s="22" t="n">
         <v>4303</v>
       </c>
-      <c r="D758" s="32" t="s">
+      <c r="D758" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E758" s="22" t="n">
@@ -27972,7 +27961,7 @@
       <c r="C759" s="22" t="n">
         <v>4304</v>
       </c>
-      <c r="D759" s="32" t="s">
+      <c r="D759" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E759" s="22" t="n">
@@ -28001,7 +27990,7 @@
       <c r="C760" s="22" t="n">
         <v>4306</v>
       </c>
-      <c r="D760" s="32" t="s">
+      <c r="D760" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E760" s="22" t="n">
@@ -28030,7 +28019,7 @@
       <c r="C761" s="22" t="n">
         <v>4307</v>
       </c>
-      <c r="D761" s="32" t="s">
+      <c r="D761" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E761" s="22" t="n">
@@ -28059,7 +28048,7 @@
       <c r="C762" s="22" t="n">
         <v>4308</v>
       </c>
-      <c r="D762" s="32" t="s">
+      <c r="D762" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E762" s="22" t="n">
@@ -28088,7 +28077,7 @@
       <c r="C763" s="22" t="n">
         <v>4309</v>
       </c>
-      <c r="D763" s="32" t="s">
+      <c r="D763" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E763" s="22" t="n">
@@ -28117,7 +28106,7 @@
       <c r="C764" s="22" t="n">
         <v>4310</v>
       </c>
-      <c r="D764" s="32" t="s">
+      <c r="D764" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E764" s="22" t="n">
@@ -28146,7 +28135,7 @@
       <c r="C765" s="22" t="n">
         <v>4311</v>
       </c>
-      <c r="D765" s="32" t="s">
+      <c r="D765" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E765" s="22" t="n">
@@ -28175,7 +28164,7 @@
       <c r="C766" s="24" t="s">
         <v>1344</v>
       </c>
-      <c r="D766" s="32"/>
+      <c r="D766" s="31"/>
       <c r="E766" s="22"/>
       <c r="G766" s="22" t="s">
         <v>117</v>
@@ -28191,7 +28180,7 @@
       <c r="C767" s="22" t="n">
         <v>4320</v>
       </c>
-      <c r="D767" s="32" t="s">
+      <c r="D767" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E767" s="22"/>
@@ -28212,7 +28201,7 @@
       <c r="C768" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="D768" s="32" t="s">
+      <c r="D768" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E768" s="22" t="n">
@@ -28241,7 +28230,7 @@
       <c r="C769" s="22" t="n">
         <v>4401</v>
       </c>
-      <c r="D769" s="32" t="s">
+      <c r="D769" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E769" s="22" t="n">
@@ -28270,7 +28259,7 @@
       <c r="C770" s="22" t="n">
         <v>4402</v>
       </c>
-      <c r="D770" s="32" t="s">
+      <c r="D770" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E770" s="22" t="n">
@@ -28299,7 +28288,7 @@
       <c r="C771" s="22" t="n">
         <v>4403</v>
       </c>
-      <c r="D771" s="32" t="s">
+      <c r="D771" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E771" s="22" t="n">
@@ -28328,7 +28317,7 @@
       <c r="C772" s="22" t="n">
         <v>4404</v>
       </c>
-      <c r="D772" s="32" t="s">
+      <c r="D772" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E772" s="22" t="n">
@@ -28357,7 +28346,7 @@
       <c r="C773" s="22" t="n">
         <v>4406</v>
       </c>
-      <c r="D773" s="32" t="s">
+      <c r="D773" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E773" s="22" t="n">
@@ -28386,7 +28375,7 @@
       <c r="C774" s="22" t="n">
         <v>4408</v>
       </c>
-      <c r="D774" s="32" t="s">
+      <c r="D774" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E774" s="22" t="n">
@@ -28415,7 +28404,7 @@
       <c r="C775" s="22" t="n">
         <v>4409</v>
       </c>
-      <c r="D775" s="32" t="s">
+      <c r="D775" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E775" s="22" t="n">
@@ -28444,7 +28433,7 @@
       <c r="C776" s="22" t="n">
         <v>4410</v>
       </c>
-      <c r="D776" s="32" t="s">
+      <c r="D776" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E776" s="22" t="n">
@@ -28473,7 +28462,7 @@
       <c r="C777" s="22" t="n">
         <v>4411</v>
       </c>
-      <c r="D777" s="32" t="s">
+      <c r="D777" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E777" s="22" t="n">
@@ -28502,7 +28491,7 @@
       <c r="C778" s="22" t="n">
         <v>4412</v>
       </c>
-      <c r="D778" s="32" t="s">
+      <c r="D778" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E778" s="22" t="n">
@@ -28531,7 +28520,7 @@
       <c r="C779" s="22" t="n">
         <v>4413</v>
       </c>
-      <c r="D779" s="32" t="s">
+      <c r="D779" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E779" s="22" t="n">
@@ -28560,7 +28549,7 @@
       <c r="C780" s="24" t="s">
         <v>1347</v>
       </c>
-      <c r="D780" s="32"/>
+      <c r="D780" s="31"/>
       <c r="E780" s="22"/>
       <c r="G780" s="22" t="s">
         <v>117</v>
@@ -28576,7 +28565,7 @@
       <c r="C781" s="22" t="n">
         <v>4420</v>
       </c>
-      <c r="D781" s="32" t="s">
+      <c r="D781" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E781" s="22"/>
@@ -28597,7 +28586,7 @@
       <c r="C782" s="22" t="n">
         <v>4500</v>
       </c>
-      <c r="D782" s="32" t="s">
+      <c r="D782" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E782" s="22" t="n">
@@ -28626,7 +28615,7 @@
       <c r="C783" s="22" t="n">
         <v>4501</v>
       </c>
-      <c r="D783" s="32" t="s">
+      <c r="D783" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E783" s="22" t="n">
@@ -28655,7 +28644,7 @@
       <c r="C784" s="22" t="n">
         <v>4502</v>
       </c>
-      <c r="D784" s="32" t="s">
+      <c r="D784" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E784" s="22" t="n">
@@ -28684,7 +28673,7 @@
       <c r="C785" s="22" t="n">
         <v>4503</v>
       </c>
-      <c r="D785" s="32" t="s">
+      <c r="D785" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E785" s="22" t="n">
@@ -28713,7 +28702,7 @@
       <c r="C786" s="22" t="n">
         <v>4504</v>
       </c>
-      <c r="D786" s="32" t="s">
+      <c r="D786" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E786" s="22" t="n">
@@ -28742,7 +28731,7 @@
       <c r="C787" s="22" t="n">
         <v>4505</v>
       </c>
-      <c r="D787" s="32" t="s">
+      <c r="D787" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E787" s="22" t="n">
@@ -28771,7 +28760,7 @@
       <c r="C788" s="22" t="n">
         <v>4506</v>
       </c>
-      <c r="D788" s="32" t="s">
+      <c r="D788" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E788" s="22" t="s">
@@ -28800,7 +28789,7 @@
       <c r="C789" s="22" t="n">
         <v>4507</v>
       </c>
-      <c r="D789" s="32" t="s">
+      <c r="D789" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E789" s="22" t="s">
@@ -28829,7 +28818,7 @@
       <c r="C790" s="22" t="n">
         <v>4508</v>
       </c>
-      <c r="D790" s="32" t="s">
+      <c r="D790" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E790" s="22" t="s">
@@ -28858,7 +28847,7 @@
       <c r="C791" s="22" t="n">
         <v>4509</v>
       </c>
-      <c r="D791" s="32" t="s">
+      <c r="D791" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E791" s="22" t="n">
@@ -28884,7 +28873,7 @@
       <c r="C792" s="22" t="n">
         <v>4510</v>
       </c>
-      <c r="D792" s="32" t="s">
+      <c r="D792" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E792" s="22" t="n">
@@ -28913,7 +28902,7 @@
       <c r="C793" s="22" t="n">
         <v>4511</v>
       </c>
-      <c r="D793" s="32" t="s">
+      <c r="D793" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E793" s="22" t="n">
@@ -28942,7 +28931,7 @@
       <c r="C794" s="22" t="n">
         <v>4512</v>
       </c>
-      <c r="D794" s="32" t="s">
+      <c r="D794" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E794" s="22" t="n">
@@ -28971,7 +28960,7 @@
       <c r="C795" s="22" t="n">
         <v>4513</v>
       </c>
-      <c r="D795" s="32" t="s">
+      <c r="D795" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E795" s="22" t="n">
@@ -29000,7 +28989,7 @@
       <c r="C796" s="22" t="n">
         <v>4514</v>
       </c>
-      <c r="D796" s="32" t="s">
+      <c r="D796" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E796" s="22" t="n">
@@ -29029,7 +29018,7 @@
       <c r="C797" s="22" t="n">
         <v>4515</v>
       </c>
-      <c r="D797" s="32" t="s">
+      <c r="D797" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E797" s="22" t="n">
@@ -29058,7 +29047,7 @@
       <c r="C798" s="22" t="n">
         <v>4516</v>
       </c>
-      <c r="D798" s="32" t="s">
+      <c r="D798" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E798" s="22" t="s">
@@ -29087,7 +29076,7 @@
       <c r="C799" s="22" t="n">
         <v>4517</v>
       </c>
-      <c r="D799" s="32" t="s">
+      <c r="D799" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E799" s="22" t="s">
@@ -29116,7 +29105,7 @@
       <c r="C800" s="22" t="n">
         <v>4518</v>
       </c>
-      <c r="D800" s="32" t="s">
+      <c r="D800" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E800" s="22" t="s">
@@ -29145,7 +29134,7 @@
       <c r="C801" s="22" t="n">
         <v>4519</v>
       </c>
-      <c r="D801" s="32" t="s">
+      <c r="D801" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E801" s="22" t="n">
@@ -29174,7 +29163,7 @@
       <c r="C802" s="22" t="n">
         <v>4520</v>
       </c>
-      <c r="D802" s="32" t="s">
+      <c r="D802" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E802" s="22" t="n">
@@ -29203,7 +29192,7 @@
       <c r="C803" s="22" t="n">
         <v>4521</v>
       </c>
-      <c r="D803" s="32" t="s">
+      <c r="D803" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E803" s="22" t="n">
@@ -29232,7 +29221,7 @@
       <c r="C804" s="22" t="n">
         <v>4522</v>
       </c>
-      <c r="D804" s="32" t="s">
+      <c r="D804" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E804" s="22" t="n">
@@ -29261,7 +29250,7 @@
       <c r="C805" s="22" t="n">
         <v>4523</v>
       </c>
-      <c r="D805" s="32" t="s">
+      <c r="D805" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E805" s="22" t="n">
@@ -29290,7 +29279,7 @@
       <c r="C806" s="22" t="n">
         <v>4524</v>
       </c>
-      <c r="D806" s="32" t="s">
+      <c r="D806" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E806" s="22" t="n">
@@ -29319,7 +29308,7 @@
       <c r="C807" s="22" t="n">
         <v>4525</v>
       </c>
-      <c r="D807" s="32" t="s">
+      <c r="D807" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E807" s="22" t="n">
@@ -29348,7 +29337,7 @@
       <c r="C808" s="22" t="n">
         <v>4526</v>
       </c>
-      <c r="D808" s="32" t="s">
+      <c r="D808" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E808" s="22" t="n">
@@ -29377,7 +29366,7 @@
       <c r="C809" s="22" t="n">
         <v>4527</v>
       </c>
-      <c r="D809" s="32" t="s">
+      <c r="D809" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E809" s="22" t="n">
@@ -29406,7 +29395,7 @@
       <c r="C810" s="22" t="n">
         <v>4528</v>
       </c>
-      <c r="D810" s="32" t="s">
+      <c r="D810" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E810" s="22" t="n">
@@ -29435,7 +29424,7 @@
       <c r="C811" s="22" t="n">
         <v>4529</v>
       </c>
-      <c r="D811" s="32" t="s">
+      <c r="D811" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E811" s="22" t="n">
@@ -29464,7 +29453,7 @@
       <c r="C812" s="22" t="n">
         <v>4530</v>
       </c>
-      <c r="D812" s="32" t="s">
+      <c r="D812" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E812" s="22" t="n">
@@ -29493,7 +29482,7 @@
       <c r="C813" s="22" t="n">
         <v>4531</v>
       </c>
-      <c r="D813" s="32" t="s">
+      <c r="D813" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E813" s="22" t="n">
@@ -29522,7 +29511,7 @@
       <c r="C814" s="22" t="n">
         <v>4532</v>
       </c>
-      <c r="D814" s="32" t="s">
+      <c r="D814" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E814" s="22" t="n">
@@ -29551,7 +29540,7 @@
       <c r="C815" s="22" t="n">
         <v>4533</v>
       </c>
-      <c r="D815" s="32" t="s">
+      <c r="D815" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E815" s="22" t="n">
@@ -29580,7 +29569,7 @@
       <c r="C816" s="22" t="n">
         <v>4534</v>
       </c>
-      <c r="D816" s="32" t="s">
+      <c r="D816" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E816" s="22" t="n">
@@ -29609,7 +29598,7 @@
       <c r="C817" s="22" t="n">
         <v>4535</v>
       </c>
-      <c r="D817" s="32" t="s">
+      <c r="D817" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E817" s="22" t="n">
@@ -29638,7 +29627,7 @@
       <c r="C818" s="22" t="n">
         <v>4536</v>
       </c>
-      <c r="D818" s="32" t="s">
+      <c r="D818" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E818" s="22" t="n">
@@ -29667,7 +29656,7 @@
       <c r="C819" s="22" t="n">
         <v>4537</v>
       </c>
-      <c r="D819" s="32" t="s">
+      <c r="D819" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E819" s="22" t="n">
@@ -29696,7 +29685,7 @@
       <c r="C820" s="22" t="n">
         <v>4538</v>
       </c>
-      <c r="D820" s="32" t="s">
+      <c r="D820" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E820" s="22" t="n">
@@ -29725,7 +29714,7 @@
       <c r="C821" s="22" t="n">
         <v>4539</v>
       </c>
-      <c r="D821" s="32" t="s">
+      <c r="D821" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E821" s="22" t="n">
@@ -29754,7 +29743,7 @@
       <c r="C822" s="22" t="n">
         <v>4540</v>
       </c>
-      <c r="D822" s="32" t="s">
+      <c r="D822" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E822" s="22" t="n">
@@ -29783,7 +29772,7 @@
       <c r="C823" s="22" t="n">
         <v>4541</v>
       </c>
-      <c r="D823" s="32" t="s">
+      <c r="D823" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E823" s="22" t="n">
@@ -29812,7 +29801,7 @@
       <c r="C824" s="22" t="n">
         <v>4542</v>
       </c>
-      <c r="D824" s="32" t="s">
+      <c r="D824" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E824" s="22" t="n">
@@ -29841,7 +29830,7 @@
       <c r="C825" s="22" t="n">
         <v>4543</v>
       </c>
-      <c r="D825" s="32" t="s">
+      <c r="D825" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E825" s="22" t="n">
@@ -29870,7 +29859,7 @@
       <c r="C826" s="22" t="n">
         <v>4544</v>
       </c>
-      <c r="D826" s="32" t="s">
+      <c r="D826" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E826" s="22" t="n">
@@ -29899,7 +29888,7 @@
       <c r="C827" s="22" t="n">
         <v>4545</v>
       </c>
-      <c r="D827" s="32" t="s">
+      <c r="D827" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E827" s="22" t="n">
@@ -29928,7 +29917,7 @@
       <c r="C828" s="22" t="n">
         <v>4546</v>
       </c>
-      <c r="D828" s="32" t="s">
+      <c r="D828" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E828" s="22" t="n">
@@ -29957,7 +29946,7 @@
       <c r="C829" s="22" t="n">
         <v>4548</v>
       </c>
-      <c r="D829" s="32" t="s">
+      <c r="D829" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E829" s="22" t="n">
@@ -29986,7 +29975,7 @@
       <c r="C830" s="22" t="n">
         <v>4550</v>
       </c>
-      <c r="D830" s="32" t="s">
+      <c r="D830" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E830" s="22" t="n">
@@ -30015,7 +30004,7 @@
       <c r="C831" s="22" t="n">
         <v>4552</v>
       </c>
-      <c r="D831" s="32" t="s">
+      <c r="D831" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E831" s="22" t="n">
@@ -30044,7 +30033,7 @@
       <c r="C832" s="22" t="n">
         <v>4554</v>
       </c>
-      <c r="D832" s="32" t="s">
+      <c r="D832" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E832" s="22" t="n">
@@ -30073,7 +30062,7 @@
       <c r="C833" s="22" t="n">
         <v>4556</v>
       </c>
-      <c r="D833" s="32" t="s">
+      <c r="D833" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E833" s="22" t="n">
@@ -30102,7 +30091,7 @@
       <c r="C834" s="22" t="n">
         <v>4558</v>
       </c>
-      <c r="D834" s="32" t="s">
+      <c r="D834" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E834" s="22" t="n">
@@ -30131,7 +30120,7 @@
       <c r="C835" s="22" t="n">
         <v>4560</v>
       </c>
-      <c r="D835" s="32" t="s">
+      <c r="D835" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E835" s="22" t="n">
@@ -30160,7 +30149,7 @@
       <c r="C836" s="22" t="n">
         <v>4562</v>
       </c>
-      <c r="D836" s="32" t="s">
+      <c r="D836" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E836" s="22" t="n">
@@ -30189,7 +30178,7 @@
       <c r="C837" s="22" t="n">
         <v>4564</v>
       </c>
-      <c r="D837" s="32" t="s">
+      <c r="D837" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E837" s="22" t="n">
@@ -30218,7 +30207,7 @@
       <c r="C838" s="22" t="n">
         <v>4566</v>
       </c>
-      <c r="D838" s="32" t="s">
+      <c r="D838" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E838" s="22" t="n">
@@ -30247,7 +30236,7 @@
       <c r="C839" s="22" t="n">
         <v>4568</v>
       </c>
-      <c r="D839" s="32" t="s">
+      <c r="D839" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E839" s="22" t="n">
@@ -30276,7 +30265,7 @@
       <c r="C840" s="22" t="n">
         <v>4570</v>
       </c>
-      <c r="D840" s="32" t="s">
+      <c r="D840" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E840" s="22" t="n">
@@ -30305,7 +30294,7 @@
       <c r="C841" s="22" t="n">
         <v>4572</v>
       </c>
-      <c r="D841" s="32" t="s">
+      <c r="D841" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E841" s="22" t="n">
@@ -30334,7 +30323,7 @@
       <c r="C842" s="22" t="n">
         <v>4574</v>
       </c>
-      <c r="D842" s="32" t="s">
+      <c r="D842" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E842" s="22" t="n">
@@ -30363,7 +30352,7 @@
       <c r="C843" s="22" t="n">
         <v>4575</v>
       </c>
-      <c r="D843" s="32" t="s">
+      <c r="D843" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E843" s="22" t="n">
@@ -30392,7 +30381,7 @@
       <c r="C844" s="22" t="n">
         <v>4576</v>
       </c>
-      <c r="D844" s="32" t="s">
+      <c r="D844" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E844" s="22" t="n">
@@ -30421,7 +30410,7 @@
       <c r="C845" s="22" t="n">
         <v>4577</v>
       </c>
-      <c r="D845" s="32" t="s">
+      <c r="D845" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E845" s="1" t="n">
@@ -30450,7 +30439,7 @@
       <c r="C846" s="22" t="n">
         <v>4578</v>
       </c>
-      <c r="D846" s="32" t="s">
+      <c r="D846" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E846" s="22" t="n">
@@ -30483,7 +30472,7 @@
       <c r="C847" s="22" t="n">
         <v>4579</v>
       </c>
-      <c r="D847" s="32" t="s">
+      <c r="D847" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E847" s="22" t="n">
@@ -30516,7 +30505,7 @@
       <c r="C848" s="22" t="n">
         <v>4580</v>
       </c>
-      <c r="D848" s="32" t="s">
+      <c r="D848" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E848" s="22" t="n">
@@ -30549,7 +30538,7 @@
       <c r="C849" s="22" t="n">
         <v>4581</v>
       </c>
-      <c r="D849" s="32" t="s">
+      <c r="D849" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E849" s="22" t="n">
@@ -30582,7 +30571,7 @@
       <c r="C850" s="22" t="n">
         <v>4582</v>
       </c>
-      <c r="D850" s="32" t="s">
+      <c r="D850" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E850" s="22" t="n">
@@ -30615,7 +30604,7 @@
       <c r="C851" s="22" t="n">
         <v>4583</v>
       </c>
-      <c r="D851" s="32" t="s">
+      <c r="D851" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E851" s="22" t="n">
@@ -30648,7 +30637,7 @@
       <c r="C852" s="22" t="n">
         <v>4584</v>
       </c>
-      <c r="D852" s="32" t="s">
+      <c r="D852" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E852" s="22" t="n">
@@ -30681,7 +30670,7 @@
       <c r="C853" s="22" t="n">
         <v>4585</v>
       </c>
-      <c r="D853" s="32" t="s">
+      <c r="D853" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E853" s="22" t="n">
@@ -30714,7 +30703,7 @@
       <c r="C854" s="22" t="n">
         <v>4586</v>
       </c>
-      <c r="D854" s="32" t="s">
+      <c r="D854" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E854" s="22" t="n">
@@ -30747,7 +30736,7 @@
       <c r="C855" s="22" t="n">
         <v>4587</v>
       </c>
-      <c r="D855" s="32" t="s">
+      <c r="D855" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E855" s="22" t="n">
@@ -30780,7 +30769,7 @@
       <c r="C856" s="22" t="n">
         <v>4588</v>
       </c>
-      <c r="D856" s="32" t="s">
+      <c r="D856" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E856" s="22" t="n">
@@ -30813,7 +30802,7 @@
       <c r="C857" s="22" t="n">
         <v>4589</v>
       </c>
-      <c r="D857" s="32" t="s">
+      <c r="D857" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E857" s="22" t="n">
@@ -30846,7 +30835,7 @@
       <c r="C858" s="22" t="n">
         <v>4590</v>
       </c>
-      <c r="D858" s="32" t="s">
+      <c r="D858" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E858" s="22" t="n">
@@ -30879,7 +30868,7 @@
       <c r="C859" s="22" t="n">
         <v>4591</v>
       </c>
-      <c r="D859" s="32" t="s">
+      <c r="D859" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E859" s="22" t="n">
@@ -30912,7 +30901,7 @@
       <c r="C860" s="22" t="n">
         <v>4592</v>
       </c>
-      <c r="D860" s="32" t="s">
+      <c r="D860" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E860" s="22" t="n">
@@ -30945,7 +30934,7 @@
       <c r="C861" s="22" t="n">
         <v>4593</v>
       </c>
-      <c r="D861" s="32" t="s">
+      <c r="D861" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E861" s="22" t="n">
@@ -30978,7 +30967,7 @@
       <c r="C862" s="1" t="n">
         <v>4594</v>
       </c>
-      <c r="D862" s="32" t="s">
+      <c r="D862" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E862" s="1" t="n">
@@ -31007,7 +30996,7 @@
       <c r="C863" s="1" t="n">
         <v>4595</v>
       </c>
-      <c r="D863" s="32" t="s">
+      <c r="D863" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E863" s="1" t="n">
@@ -31036,7 +31025,7 @@
       <c r="C864" s="1" t="n">
         <v>4596</v>
       </c>
-      <c r="D864" s="32" t="s">
+      <c r="D864" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E864" s="1" t="n">
@@ -31065,7 +31054,7 @@
       <c r="C865" s="1" t="n">
         <v>4597</v>
       </c>
-      <c r="D865" s="32" t="s">
+      <c r="D865" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E865" s="1" t="n">
@@ -31094,7 +31083,7 @@
       <c r="C866" s="1" t="n">
         <v>4598</v>
       </c>
-      <c r="D866" s="32" t="s">
+      <c r="D866" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E866" s="1" t="n">
@@ -31123,7 +31112,7 @@
       <c r="C867" s="1" t="n">
         <v>4599</v>
       </c>
-      <c r="D867" s="32" t="s">
+      <c r="D867" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E867" s="1" t="n">
@@ -31152,7 +31141,7 @@
       <c r="C868" s="1" t="n">
         <v>4600</v>
       </c>
-      <c r="D868" s="32" t="s">
+      <c r="D868" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E868" s="1" t="n">
@@ -31181,7 +31170,7 @@
       <c r="C869" s="1" t="n">
         <v>4601</v>
       </c>
-      <c r="D869" s="32" t="s">
+      <c r="D869" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E869" s="1" t="n">
@@ -31210,7 +31199,7 @@
       <c r="C870" s="1" t="n">
         <v>4602</v>
       </c>
-      <c r="D870" s="32" t="s">
+      <c r="D870" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E870" s="1" t="n">
@@ -31271,7 +31260,7 @@
       <c r="C872" s="1" t="n">
         <v>4605</v>
       </c>
-      <c r="D872" s="32" t="s">
+      <c r="D872" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E872" s="1" t="n">
@@ -31300,7 +31289,7 @@
       <c r="C873" s="1" t="n">
         <v>4606</v>
       </c>
-      <c r="D873" s="32" t="s">
+      <c r="D873" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E873" s="1" t="n">
@@ -31329,7 +31318,7 @@
       <c r="C874" s="1" t="n">
         <v>4607</v>
       </c>
-      <c r="D874" s="32" t="s">
+      <c r="D874" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="1" t="n">
@@ -31358,7 +31347,7 @@
       <c r="C875" s="1" t="n">
         <v>4608</v>
       </c>
-      <c r="D875" s="32" t="s">
+      <c r="D875" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E875" s="1" t="n">
@@ -31387,7 +31376,7 @@
       <c r="C876" s="1" t="n">
         <v>4609</v>
       </c>
-      <c r="D876" s="32" t="s">
+      <c r="D876" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E876" s="1" t="n">
@@ -31416,7 +31405,7 @@
       <c r="C877" s="1" t="n">
         <v>4610</v>
       </c>
-      <c r="D877" s="32" t="s">
+      <c r="D877" s="31" t="s">
         <v>136</v>
       </c>
       <c r="E877" s="1" t="n">
@@ -31445,7 +31434,7 @@
       <c r="C878" s="1" t="n">
         <v>4612</v>
       </c>
-      <c r="D878" s="32" t="s">
+      <c r="D878" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E878" s="1" t="n">
@@ -31474,7 +31463,7 @@
       <c r="C879" s="1" t="n">
         <v>4613</v>
       </c>
-      <c r="D879" s="32" t="s">
+      <c r="D879" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E879" s="1" t="n">
@@ -31503,7 +31492,7 @@
       <c r="C880" s="1" t="n">
         <v>4614</v>
       </c>
-      <c r="D880" s="32" t="s">
+      <c r="D880" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E880" s="1" t="n">
@@ -31532,7 +31521,7 @@
       <c r="C881" s="1" t="n">
         <v>4615</v>
       </c>
-      <c r="D881" s="32" t="s">
+      <c r="D881" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E881" s="1" t="n">
@@ -31561,7 +31550,7 @@
       <c r="C882" s="23" t="s">
         <v>1409</v>
       </c>
-      <c r="D882" s="32"/>
+      <c r="D882" s="31"/>
     </row>
     <row r="883" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
@@ -31573,7 +31562,7 @@
       <c r="C883" s="1" t="n">
         <v>4620</v>
       </c>
-      <c r="D883" s="32" t="s">
+      <c r="D883" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E883" s="22" t="n">
@@ -31602,7 +31591,7 @@
       <c r="C884" s="1" t="n">
         <v>4621</v>
       </c>
-      <c r="D884" s="32"/>
+      <c r="D884" s="31"/>
       <c r="E884" s="22"/>
       <c r="G884" s="22" t="s">
         <v>117</v>
@@ -31620,7 +31609,7 @@
       <c r="C885" s="1" t="n">
         <v>4622</v>
       </c>
-      <c r="D885" s="32" t="s">
+      <c r="D885" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E885" s="22"/>
@@ -31758,7 +31747,7 @@
       <c r="C890" s="1" t="n">
         <v>4700</v>
       </c>
-      <c r="D890" s="32" t="s">
+      <c r="D890" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E890" s="1" t="n">
@@ -31787,7 +31776,7 @@
       <c r="C891" s="1" t="n">
         <v>4701</v>
       </c>
-      <c r="D891" s="32" t="s">
+      <c r="D891" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E891" s="1" t="n">
@@ -31816,7 +31805,7 @@
       <c r="C892" s="1" t="n">
         <v>4702</v>
       </c>
-      <c r="D892" s="32" t="s">
+      <c r="D892" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E892" s="1" t="n">
@@ -31845,7 +31834,7 @@
       <c r="C893" s="1" t="n">
         <v>4703</v>
       </c>
-      <c r="D893" s="32" t="s">
+      <c r="D893" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E893" s="1" t="n">
@@ -31874,7 +31863,7 @@
       <c r="C894" s="1" t="n">
         <v>4704</v>
       </c>
-      <c r="D894" s="32" t="s">
+      <c r="D894" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E894" s="1" t="n">
@@ -31903,7 +31892,7 @@
       <c r="C895" s="22" t="n">
         <v>4800</v>
       </c>
-      <c r="D895" s="32" t="s">
+      <c r="D895" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E895" s="22" t="n">
@@ -31929,7 +31918,7 @@
       <c r="C896" s="22" t="n">
         <v>4801</v>
       </c>
-      <c r="D896" s="32" t="s">
+      <c r="D896" s="31" t="s">
         <v>155</v>
       </c>
       <c r="E896" s="22" t="n">
@@ -31955,7 +31944,7 @@
       <c r="C897" s="22" t="n">
         <v>4803</v>
       </c>
-      <c r="D897" s="32" t="s">
+      <c r="D897" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E897" s="22" t="n">
@@ -31984,7 +31973,7 @@
       <c r="C898" s="22" t="n">
         <v>4804</v>
       </c>
-      <c r="D898" s="32" t="s">
+      <c r="D898" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E898" s="22" t="n">
@@ -32013,7 +32002,7 @@
       <c r="C899" s="22" t="n">
         <v>4805</v>
       </c>
-      <c r="D899" s="32" t="s">
+      <c r="D899" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E899" s="22" t="n">
@@ -32042,7 +32031,7 @@
       <c r="C900" s="22" t="n">
         <v>4806</v>
       </c>
-      <c r="D900" s="32" t="s">
+      <c r="D900" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E900" s="22" t="n">
@@ -32071,7 +32060,7 @@
       <c r="C901" s="22" t="n">
         <v>4807</v>
       </c>
-      <c r="D901" s="32" t="s">
+      <c r="D901" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E901" s="22" t="n">
@@ -32100,7 +32089,7 @@
       <c r="C902" s="22" t="n">
         <v>4808</v>
       </c>
-      <c r="D902" s="32" t="s">
+      <c r="D902" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E902" s="22" t="n">
@@ -32129,7 +32118,7 @@
       <c r="C903" s="22" t="n">
         <v>4809</v>
       </c>
-      <c r="D903" s="32" t="s">
+      <c r="D903" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E903" s="22" t="n">
@@ -32158,7 +32147,7 @@
       <c r="C904" s="22" t="n">
         <v>4810</v>
       </c>
-      <c r="D904" s="32" t="s">
+      <c r="D904" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E904" s="22" t="n">
@@ -32187,7 +32176,7 @@
       <c r="C905" s="22" t="n">
         <v>4811</v>
       </c>
-      <c r="D905" s="32" t="s">
+      <c r="D905" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E905" s="22" t="n">
@@ -32216,7 +32205,7 @@
       <c r="C906" s="24" t="s">
         <v>1426</v>
       </c>
-      <c r="D906" s="32"/>
+      <c r="D906" s="31"/>
       <c r="E906" s="22"/>
       <c r="G906" s="22" t="s">
         <v>117</v>
@@ -32233,7 +32222,7 @@
       <c r="C907" s="22" t="n">
         <v>4820</v>
       </c>
-      <c r="D907" s="32" t="s">
+      <c r="D907" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E907" s="22"/>
@@ -32255,7 +32244,7 @@
       <c r="C908" s="22" t="n">
         <v>4900</v>
       </c>
-      <c r="D908" s="32" t="s">
+      <c r="D908" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E908" s="22" t="n">
@@ -32284,7 +32273,7 @@
       <c r="C909" s="22" t="n">
         <v>4901</v>
       </c>
-      <c r="D909" s="32" t="s">
+      <c r="D909" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E909" s="22" t="n">
@@ -32313,7 +32302,7 @@
       <c r="C910" s="22" t="n">
         <v>4902</v>
       </c>
-      <c r="D910" s="32" t="s">
+      <c r="D910" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E910" s="22" t="n">
@@ -32342,7 +32331,7 @@
       <c r="C911" s="22" t="n">
         <v>4903</v>
       </c>
-      <c r="D911" s="32" t="s">
+      <c r="D911" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E911" s="22" t="n">
@@ -32371,7 +32360,7 @@
       <c r="C912" s="22" t="n">
         <v>4904</v>
       </c>
-      <c r="D912" s="32" t="s">
+      <c r="D912" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E912" s="22" t="n">
@@ -32400,7 +32389,7 @@
       <c r="C913" s="22" t="n">
         <v>4905</v>
       </c>
-      <c r="D913" s="32" t="s">
+      <c r="D913" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E913" s="22" t="n">
@@ -32429,7 +32418,7 @@
       <c r="C914" s="22" t="n">
         <v>4906</v>
       </c>
-      <c r="D914" s="32" t="s">
+      <c r="D914" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E914" s="22" t="n">
@@ -32458,7 +32447,7 @@
       <c r="C915" s="22" t="n">
         <v>4907</v>
       </c>
-      <c r="D915" s="32" t="s">
+      <c r="D915" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E915" s="22" t="s">
@@ -32487,7 +32476,7 @@
       <c r="C916" s="22" t="n">
         <v>4908</v>
       </c>
-      <c r="D916" s="32" t="s">
+      <c r="D916" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E916" s="22" t="s">
@@ -32516,7 +32505,7 @@
       <c r="C917" s="22" t="n">
         <v>4909</v>
       </c>
-      <c r="D917" s="32" t="s">
+      <c r="D917" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E917" s="22" t="s">
@@ -32545,7 +32534,7 @@
       <c r="C918" s="22" t="n">
         <v>4910</v>
       </c>
-      <c r="D918" s="32" t="s">
+      <c r="D918" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E918" s="22" t="n">
@@ -32574,7 +32563,7 @@
       <c r="C919" s="22" t="n">
         <v>4911</v>
       </c>
-      <c r="D919" s="32" t="s">
+      <c r="D919" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E919" s="22" t="n">
@@ -32603,7 +32592,7 @@
       <c r="C920" s="22" t="n">
         <v>4912</v>
       </c>
-      <c r="D920" s="32" t="s">
+      <c r="D920" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E920" s="22" t="n">
@@ -32632,7 +32621,7 @@
       <c r="C921" s="22" t="n">
         <v>4913</v>
       </c>
-      <c r="D921" s="32" t="s">
+      <c r="D921" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E921" s="22" t="n">
@@ -32661,7 +32650,7 @@
       <c r="C922" s="22" t="n">
         <v>4914</v>
       </c>
-      <c r="D922" s="32" t="s">
+      <c r="D922" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E922" s="22" t="n">
@@ -32690,7 +32679,7 @@
       <c r="C923" s="22" t="n">
         <v>4915</v>
       </c>
-      <c r="D923" s="32" t="s">
+      <c r="D923" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E923" s="22" t="n">
@@ -32719,7 +32708,7 @@
       <c r="C924" s="22" t="n">
         <v>4916</v>
       </c>
-      <c r="D924" s="32" t="s">
+      <c r="D924" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E924" s="22" t="n">
@@ -32748,7 +32737,7 @@
       <c r="C925" s="22" t="n">
         <v>4917</v>
       </c>
-      <c r="D925" s="32" t="s">
+      <c r="D925" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E925" s="22" t="s">
@@ -32777,7 +32766,7 @@
       <c r="C926" s="22" t="n">
         <v>4918</v>
       </c>
-      <c r="D926" s="32" t="s">
+      <c r="D926" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E926" s="22" t="s">
@@ -32806,7 +32795,7 @@
       <c r="C927" s="22" t="n">
         <v>4919</v>
       </c>
-      <c r="D927" s="32" t="s">
+      <c r="D927" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E927" s="22" t="s">
@@ -32835,7 +32824,7 @@
       <c r="C928" s="22" t="n">
         <v>4920</v>
       </c>
-      <c r="D928" s="32" t="s">
+      <c r="D928" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E928" s="22" t="n">
@@ -32864,7 +32853,7 @@
       <c r="C929" s="22" t="n">
         <v>4921</v>
       </c>
-      <c r="D929" s="32" t="s">
+      <c r="D929" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E929" s="22" t="n">
@@ -32893,7 +32882,7 @@
       <c r="C930" s="22" t="n">
         <v>4922</v>
       </c>
-      <c r="D930" s="32" t="s">
+      <c r="D930" s="31" t="s">
         <v>136</v>
       </c>
       <c r="E930" s="22" t="n">
@@ -32922,7 +32911,7 @@
       <c r="C931" s="22" t="n">
         <v>4924</v>
       </c>
-      <c r="D931" s="32" t="s">
+      <c r="D931" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E931" s="22" t="n">
@@ -32951,7 +32940,7 @@
       <c r="C932" s="1" t="n">
         <v>4925</v>
       </c>
-      <c r="D932" s="32" t="s">
+      <c r="D932" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E932" s="1" t="n">
@@ -33216,7 +33205,7 @@
       <c r="C943" s="25" t="n">
         <v>5200</v>
       </c>
-      <c r="D943" s="32" t="s">
+      <c r="D943" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E943" s="25" t="n">
@@ -33242,7 +33231,7 @@
       <c r="C944" s="25" t="n">
         <v>5201</v>
       </c>
-      <c r="D944" s="32" t="s">
+      <c r="D944" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E944" s="25" t="n">
@@ -33268,7 +33257,7 @@
       <c r="C945" s="25" t="n">
         <v>5202</v>
       </c>
-      <c r="D945" s="32" t="s">
+      <c r="D945" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E945" s="25" t="n">
@@ -33294,7 +33283,7 @@
       <c r="C946" s="25" t="n">
         <v>5203</v>
       </c>
-      <c r="D946" s="32" t="s">
+      <c r="D946" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E946" s="25" t="n">
@@ -33320,7 +33309,7 @@
       <c r="C947" s="25" t="n">
         <v>5204</v>
       </c>
-      <c r="D947" s="32" t="s">
+      <c r="D947" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E947" s="25" t="n">
@@ -33349,7 +33338,7 @@
       <c r="C948" s="25" t="n">
         <v>5205</v>
       </c>
-      <c r="D948" s="32" t="s">
+      <c r="D948" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E948" s="25" t="n">
@@ -33378,7 +33367,7 @@
       <c r="C949" s="25" t="n">
         <v>5206</v>
       </c>
-      <c r="D949" s="32" t="s">
+      <c r="D949" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E949" s="25" t="n">
@@ -33407,7 +33396,7 @@
       <c r="C950" s="25" t="n">
         <v>5207</v>
       </c>
-      <c r="D950" s="32" t="s">
+      <c r="D950" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E950" s="25" t="n">
@@ -33436,7 +33425,7 @@
       <c r="C951" s="25" t="n">
         <v>5208</v>
       </c>
-      <c r="D951" s="32" t="s">
+      <c r="D951" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E951" s="25" t="n">
@@ -33465,7 +33454,7 @@
       <c r="C952" s="25" t="n">
         <v>5209</v>
       </c>
-      <c r="D952" s="32" t="s">
+      <c r="D952" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E952" s="25" t="s">
@@ -33494,7 +33483,7 @@
       <c r="C953" s="25" t="n">
         <v>5210</v>
       </c>
-      <c r="D953" s="32" t="s">
+      <c r="D953" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E953" s="25" t="n">
@@ -33523,7 +33512,7 @@
       <c r="C954" s="25" t="n">
         <v>5211</v>
       </c>
-      <c r="D954" s="32" t="s">
+      <c r="D954" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E954" s="25" t="n">
@@ -33552,7 +33541,7 @@
       <c r="C955" s="25" t="n">
         <v>5212</v>
       </c>
-      <c r="D955" s="32" t="s">
+      <c r="D955" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E955" s="25" t="n">
@@ -33581,7 +33570,7 @@
       <c r="C956" s="25" t="n">
         <v>5213</v>
       </c>
-      <c r="D956" s="32" t="s">
+      <c r="D956" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E956" s="25" t="n">
@@ -33610,7 +33599,7 @@
       <c r="C957" s="25" t="n">
         <v>5214</v>
       </c>
-      <c r="D957" s="32" t="s">
+      <c r="D957" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E957" s="25" t="n">
@@ -33639,7 +33628,7 @@
       <c r="C958" s="25" t="n">
         <v>5215</v>
       </c>
-      <c r="D958" s="32" t="s">
+      <c r="D958" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E958" s="25" t="n">
@@ -33668,7 +33657,7 @@
       <c r="C959" s="25" t="n">
         <v>5216</v>
       </c>
-      <c r="D959" s="32" t="s">
+      <c r="D959" s="31" t="s">
         <v>59</v>
       </c>
       <c r="E959" s="25" t="n">
@@ -33697,7 +33686,7 @@
       <c r="C960" s="25" t="n">
         <v>5217</v>
       </c>
-      <c r="D960" s="32" t="s">
+      <c r="D960" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E960" s="25" t="n">
@@ -33720,7 +33709,7 @@
       <c r="C961" s="25" t="n">
         <v>5218</v>
       </c>
-      <c r="D961" s="32" t="s">
+      <c r="D961" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E961" s="25" t="n">
@@ -33746,7 +33735,7 @@
       <c r="C962" s="25" t="n">
         <v>5234</v>
       </c>
-      <c r="D962" s="32" t="s">
+      <c r="D962" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E962" s="25" t="n">
@@ -33769,7 +33758,7 @@
       <c r="C963" s="25" t="n">
         <v>5250</v>
       </c>
-      <c r="D963" s="32" t="s">
+      <c r="D963" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E963" s="25" t="n">
@@ -33792,7 +33781,7 @@
       <c r="C964" s="25" t="n">
         <v>5266</v>
       </c>
-      <c r="D964" s="32" t="s">
+      <c r="D964" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E964" s="25" t="n">
@@ -33815,7 +33804,7 @@
       <c r="C965" s="25" t="n">
         <v>5282</v>
       </c>
-      <c r="D965" s="32" t="s">
+      <c r="D965" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E965" s="25" t="n">
@@ -33838,7 +33827,7 @@
       <c r="C966" s="25" t="n">
         <v>5298</v>
       </c>
-      <c r="D966" s="32" t="s">
+      <c r="D966" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E966" s="25" t="n">
@@ -33861,7 +33850,7 @@
       <c r="C967" s="25" t="n">
         <v>5314</v>
       </c>
-      <c r="D967" s="32" t="s">
+      <c r="D967" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E967" s="25" t="n">
@@ -33884,7 +33873,7 @@
       <c r="C968" s="25" t="n">
         <v>5330</v>
       </c>
-      <c r="D968" s="32" t="s">
+      <c r="D968" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="E968" s="25" t="n">
@@ -33907,7 +33896,7 @@
       <c r="C969" s="24" t="s">
         <v>1452</v>
       </c>
-      <c r="D969" s="32"/>
+      <c r="D969" s="31"/>
       <c r="E969" s="25"/>
       <c r="G969" s="25" t="s">
         <v>117</v>
@@ -33923,7 +33912,7 @@
       <c r="C970" s="25" t="n">
         <v>5350</v>
       </c>
-      <c r="D970" s="32" t="s">
+      <c r="D970" s="31" t="s">
         <v>440</v>
       </c>
       <c r="E970" s="25"/>
@@ -33944,7 +33933,7 @@
       <c r="C971" s="1" t="n">
         <v>5400</v>
       </c>
-      <c r="D971" s="32" t="s">
+      <c r="D971" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E971" s="1" t="n">
@@ -33973,7 +33962,7 @@
       <c r="C972" s="1" t="n">
         <v>5401</v>
       </c>
-      <c r="D972" s="32" t="s">
+      <c r="D972" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E972" s="1" t="n">
@@ -34002,7 +33991,7 @@
       <c r="C973" s="1" t="n">
         <v>5402</v>
       </c>
-      <c r="D973" s="32" t="s">
+      <c r="D973" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E973" s="1" t="n">
@@ -34031,7 +34020,7 @@
       <c r="C974" s="1" t="n">
         <v>5403</v>
       </c>
-      <c r="D974" s="32" t="s">
+      <c r="D974" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E974" s="1" t="n">
@@ -34057,7 +34046,7 @@
       <c r="C975" s="1" t="n">
         <v>5404</v>
       </c>
-      <c r="D975" s="32" t="s">
+      <c r="D975" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E975" s="1" t="n">
@@ -34086,7 +34075,7 @@
       <c r="C976" s="1" t="n">
         <v>5405</v>
       </c>
-      <c r="D976" s="32" t="s">
+      <c r="D976" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E976" s="1" t="n">
@@ -34115,7 +34104,7 @@
       <c r="C977" s="1" t="n">
         <v>5406</v>
       </c>
-      <c r="D977" s="32" t="s">
+      <c r="D977" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E977" s="1" t="n">
@@ -34144,7 +34133,7 @@
       <c r="C978" s="1" t="n">
         <v>5407</v>
       </c>
-      <c r="D978" s="32" t="s">
+      <c r="D978" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E978" s="1" t="n">
@@ -34173,7 +34162,7 @@
       <c r="C979" s="1" t="n">
         <v>5420</v>
       </c>
-      <c r="D979" s="32" t="s">
+      <c r="D979" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E979" s="1" t="n">
@@ -34202,7 +34191,7 @@
       <c r="C980" s="1" t="n">
         <v>5421</v>
       </c>
-      <c r="D980" s="32" t="s">
+      <c r="D980" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E980" s="1" t="n">
@@ -34231,7 +34220,7 @@
       <c r="C981" s="1" t="n">
         <v>5422</v>
       </c>
-      <c r="D981" s="32" t="s">
+      <c r="D981" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E981" s="1" t="n">
@@ -34260,7 +34249,7 @@
       <c r="C982" s="1" t="n">
         <v>5423</v>
       </c>
-      <c r="D982" s="32" t="s">
+      <c r="D982" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E982" s="1" t="n">
@@ -34289,7 +34278,7 @@
       <c r="C983" s="1" t="n">
         <v>5424</v>
       </c>
-      <c r="D983" s="32" t="s">
+      <c r="D983" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E983" s="1" t="n">
@@ -34318,7 +34307,7 @@
       <c r="C984" s="1" t="n">
         <v>5425</v>
       </c>
-      <c r="D984" s="32" t="s">
+      <c r="D984" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E984" s="1" t="n">
@@ -34347,7 +34336,7 @@
       <c r="C985" s="1" t="n">
         <v>5426</v>
       </c>
-      <c r="D985" s="32" t="s">
+      <c r="D985" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E985" s="1" t="n">
@@ -34376,7 +34365,7 @@
       <c r="C986" s="1" t="n">
         <v>5427</v>
       </c>
-      <c r="D986" s="32" t="s">
+      <c r="D986" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E986" s="1" t="n">
@@ -34431,7 +34420,7 @@
       <c r="C988" s="1" t="n">
         <v>5430</v>
       </c>
-      <c r="D988" s="32" t="s">
+      <c r="D988" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E988" s="1" t="n">
@@ -34910,58 +34899,58 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>1524</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>1525</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="33" t="s">
         <v>1526</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="34" t="s">
         <v>1527</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="34" t="s">
         <v>1528</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="34" t="s">
         <v>1529</v>
       </c>
     </row>
@@ -35129,24 +35118,24 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="33" t="n">
         <v>223</v>
       </c>
-      <c r="B28" s="34" t="n">
+      <c r="B28" s="33" t="n">
         <v>277</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="33" t="s">
         <v>1531</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="n">
+      <c r="A29" s="33" t="n">
         <v>224</v>
       </c>
-      <c r="B29" s="34" t="n">
+      <c r="B29" s="33" t="n">
         <v>278</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="33" t="s">
         <v>1532</v>
       </c>
     </row>
@@ -35162,57 +35151,57 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34" t="n">
+      <c r="A31" s="33" t="n">
         <v>226</v>
       </c>
-      <c r="B31" s="34" t="n">
+      <c r="B31" s="33" t="n">
         <v>279</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="33" t="s">
         <v>1534</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="33" t="n">
         <v>227</v>
       </c>
-      <c r="B32" s="34" t="n">
+      <c r="B32" s="33" t="n">
         <v>276</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="33" t="s">
         <v>1535</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34" t="n">
+      <c r="A33" s="33" t="n">
         <v>228</v>
       </c>
-      <c r="B33" s="34" t="n">
+      <c r="B33" s="33" t="n">
         <v>275</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="33" t="s">
         <v>1536</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="33" t="n">
         <v>229</v>
       </c>
-      <c r="B34" s="34" t="n">
+      <c r="B34" s="33" t="n">
         <v>274</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="33" t="s">
         <v>1537</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="n">
+      <c r="A35" s="33" t="n">
         <v>230</v>
       </c>
-      <c r="B35" s="34" t="n">
+      <c r="B35" s="33" t="n">
         <v>273</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" s="33" t="s">
         <v>1538</v>
       </c>
     </row>
@@ -35316,35 +35305,35 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34" t="n">
+      <c r="A45" s="33" t="n">
         <v>242</v>
       </c>
-      <c r="B45" s="34" t="n">
+      <c r="B45" s="33" t="n">
         <v>261</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" s="33" t="s">
         <v>1548</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34" t="n">
+      <c r="A46" s="33" t="n">
         <v>243</v>
       </c>
-      <c r="B46" s="34" t="n">
+      <c r="B46" s="33" t="n">
         <v>260</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" s="33" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="34" t="n">
+      <c r="A47" s="33" t="n">
         <v>244</v>
       </c>
-      <c r="B47" s="34" t="n">
+      <c r="B47" s="33" t="n">
         <v>259</v>
       </c>
-      <c r="C47" s="34"/>
+      <c r="C47" s="33"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="n">
@@ -35353,7 +35342,7 @@
       <c r="B48" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" s="33" t="s">
         <v>1550</v>
       </c>
     </row>
@@ -35643,7 +35632,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="35" t="s">
         <v>1602</v>
       </c>
     </row>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7166" uniqueCount="1803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7167" uniqueCount="1805">
   <si>
     <t xml:space="preserve">NOTE: Use unit-id 100 for the com.victronenergy.system data, for more information see FAQ.</t>
   </si>
@@ -3949,6 +3949,9 @@
   </si>
   <si>
     <t xml:space="preserve">/StartStop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0=AC output;1=AC input</t>
   </si>
   <si>
     <t xml:space="preserve">Session Time</t>
@@ -5437,6 +5440,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fix registers 2724 and 4929 incorrectly implemented read-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix the enumerated values for EVCharger position (register 3827)</t>
   </si>
 </sst>
 </file>
@@ -25491,7 +25497,7 @@
         <v>23</v>
       </c>
       <c r="I678" s="1" t="s">
-        <v>777</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25499,7 +25505,7 @@
         <v>1291</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C679" s="1" t="n">
         <v>3828</v>
@@ -25514,7 +25520,7 @@
         <v>756</v>
       </c>
       <c r="G679" s="1" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H679" s="1" t="s">
         <v>17</v>
@@ -25557,7 +25563,7 @@
         <v>1291</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C681" s="1" t="n">
         <v>3832</v>
@@ -25569,10 +25575,10 @@
         <v>100</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G681" s="1" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H681" s="1" t="s">
         <v>17</v>
@@ -25583,7 +25589,7 @@
         <v>1291</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C682" s="1" t="n">
         <v>3834</v>
@@ -25595,10 +25601,10 @@
         <v>100</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G682" s="1" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H682" s="1" t="s">
         <v>17</v>
@@ -25609,7 +25615,7 @@
         <v>1291</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C683" s="1" t="n">
         <v>3836</v>
@@ -25641,7 +25647,7 @@
         <v>120</v>
       </c>
       <c r="C684" s="20" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="G684" s="1" t="s">
         <v>120</v>
@@ -25669,7 +25675,7 @@
     </row>
     <row r="686" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B686" s="1" t="s">
         <v>782</v>
@@ -25698,7 +25704,7 @@
     </row>
     <row r="687" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B687" s="1" t="s">
         <v>791</v>
@@ -25727,7 +25733,7 @@
     </row>
     <row r="688" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B688" s="1" t="s">
         <v>800</v>
@@ -25756,10 +25762,10 @@
     </row>
     <row r="689" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C689" s="1" t="n">
         <v>3903</v>
@@ -25776,7 +25782,7 @@
     </row>
     <row r="690" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>778</v>
@@ -25805,7 +25811,7 @@
     </row>
     <row r="691" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B691" s="1" t="s">
         <v>780</v>
@@ -25814,7 +25820,7 @@
         <v>3911</v>
       </c>
       <c r="D691" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E691" s="1" t="n">
         <v>10</v>
@@ -25834,7 +25840,7 @@
     </row>
     <row r="692" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>787</v>
@@ -25863,7 +25869,7 @@
     </row>
     <row r="693" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B693" s="1" t="s">
         <v>789</v>
@@ -25872,7 +25878,7 @@
         <v>3913</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E693" s="1" t="n">
         <v>10</v>
@@ -25892,7 +25898,7 @@
     </row>
     <row r="694" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B694" s="1" t="s">
         <v>796</v>
@@ -25921,7 +25927,7 @@
     </row>
     <row r="695" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B695" s="1" t="s">
         <v>798</v>
@@ -25930,7 +25936,7 @@
         <v>3915</v>
       </c>
       <c r="D695" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E695" s="1" t="n">
         <v>10</v>
@@ -25950,7 +25956,7 @@
     </row>
     <row r="696" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B696" s="1" t="s">
         <v>784</v>
@@ -25979,7 +25985,7 @@
     </row>
     <row r="697" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B697" s="1" t="s">
         <v>793</v>
@@ -26008,7 +26014,7 @@
     </row>
     <row r="698" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B698" s="1" t="s">
         <v>802</v>
@@ -26037,7 +26043,7 @@
     </row>
     <row r="699" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B699" s="1" t="s">
         <v>817</v>
@@ -26066,7 +26072,7 @@
     </row>
     <row r="700" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B700" s="1" t="s">
         <v>120</v>
@@ -26077,7 +26083,7 @@
     </row>
     <row r="701" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B701" s="1" t="s">
         <v>782</v>
@@ -26106,7 +26112,7 @@
     </row>
     <row r="702" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>791</v>
@@ -26135,7 +26141,7 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B703" s="1" t="s">
         <v>800</v>
@@ -26164,7 +26170,7 @@
     </row>
     <row r="704" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B704" s="1" t="s">
         <v>954</v>
@@ -26190,7 +26196,7 @@
     </row>
     <row r="705" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B705" s="1" t="s">
         <v>957</v>
@@ -26216,7 +26222,7 @@
     </row>
     <row r="706" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B706" s="1" t="s">
         <v>959</v>
@@ -26242,7 +26248,7 @@
     </row>
     <row r="707" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B707" s="1" t="s">
         <v>961</v>
@@ -26268,13 +26274,13 @@
     </row>
     <row r="708" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B708" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C708" s="20" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="G708" s="1" t="s">
         <v>120</v>
@@ -26282,7 +26288,7 @@
     </row>
     <row r="709" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>442</v>
@@ -26302,7 +26308,7 @@
     </row>
     <row r="710" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B710" s="1" t="s">
         <v>219</v>
@@ -26331,7 +26337,7 @@
     </row>
     <row r="711" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B711" s="1" t="s">
         <v>222</v>
@@ -26360,10 +26366,10 @@
     </row>
     <row r="712" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C712" s="1" t="n">
         <v>4002</v>
@@ -26389,7 +26395,7 @@
     </row>
     <row r="713" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B713" s="1" t="s">
         <v>1198</v>
@@ -26418,10 +26424,10 @@
     </row>
     <row r="714" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C714" s="1" t="n">
         <v>4004</v>
@@ -26436,7 +26442,7 @@
         <v>1098</v>
       </c>
       <c r="G714" s="1" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H714" s="1" t="s">
         <v>17</v>
@@ -26447,7 +26453,7 @@
     </row>
     <row r="715" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B715" s="1" t="s">
         <v>543</v>
@@ -26476,7 +26482,7 @@
     </row>
     <row r="716" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B716" s="1" t="s">
         <v>545</v>
@@ -26505,10 +26511,10 @@
     </row>
     <row r="717" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C717" s="1" t="n">
         <v>4008</v>
@@ -26534,10 +26540,10 @@
     </row>
     <row r="718" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C718" s="1" t="n">
         <v>4009</v>
@@ -26563,7 +26569,7 @@
     </row>
     <row r="719" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B719" s="1" t="s">
         <v>553</v>
@@ -26592,7 +26598,7 @@
     </row>
     <row r="720" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B720" s="1" t="s">
         <v>555</v>
@@ -26621,7 +26627,7 @@
     </row>
     <row r="721" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B721" s="1" t="s">
         <v>219</v>
@@ -26650,7 +26656,7 @@
     </row>
     <row r="722" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B722" s="1" t="s">
         <v>222</v>
@@ -26679,10 +26685,10 @@
     </row>
     <row r="723" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C723" s="1" t="n">
         <v>4102</v>
@@ -26708,7 +26714,7 @@
     </row>
     <row r="724" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B724" s="1" t="s">
         <v>1198</v>
@@ -26737,10 +26743,10 @@
     </row>
     <row r="725" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C725" s="1" t="n">
         <v>4104</v>
@@ -26755,7 +26761,7 @@
         <v>1098</v>
       </c>
       <c r="G725" s="1" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H725" s="1" t="s">
         <v>17</v>
@@ -26766,7 +26772,7 @@
     </row>
     <row r="726" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B726" s="1" t="s">
         <v>543</v>
@@ -26795,7 +26801,7 @@
     </row>
     <row r="727" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B727" s="1" t="s">
         <v>545</v>
@@ -26824,10 +26830,10 @@
     </row>
     <row r="728" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C728" s="1" t="n">
         <v>4108</v>
@@ -26853,10 +26859,10 @@
     </row>
     <row r="729" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B729" s="1" t="s">
         <v>1328</v>
-      </c>
-      <c r="B729" s="1" t="s">
-        <v>1327</v>
       </c>
       <c r="C729" s="1" t="n">
         <v>4109</v>
@@ -26882,7 +26888,7 @@
     </row>
     <row r="730" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B730" s="1" t="s">
         <v>553</v>
@@ -26911,7 +26917,7 @@
     </row>
     <row r="731" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B731" s="1" t="s">
         <v>555</v>
@@ -26940,10 +26946,10 @@
     </row>
     <row r="732" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C732" s="1" t="n">
         <v>4112</v>
@@ -26964,15 +26970,15 @@
         <v>17</v>
       </c>
       <c r="I732" s="1" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="733" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C733" s="1" t="n">
         <v>4113</v>
@@ -26993,12 +26999,12 @@
         <v>17</v>
       </c>
       <c r="I733" s="1" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="734" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B734" s="1" t="s">
         <v>1148</v>
@@ -27027,10 +27033,10 @@
     </row>
     <row r="735" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C735" s="1" t="n">
         <v>4115</v>
@@ -27056,10 +27062,10 @@
     </row>
     <row r="736" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C736" s="1" t="n">
         <v>4116</v>
@@ -27074,7 +27080,7 @@
         <v>267</v>
       </c>
       <c r="G736" s="1" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H736" s="1" t="s">
         <v>17</v>
@@ -27085,10 +27091,10 @@
     </row>
     <row r="737" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C737" s="1" t="n">
         <v>4117</v>
@@ -27103,7 +27109,7 @@
         <v>220</v>
       </c>
       <c r="G737" s="1" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H737" s="1" t="s">
         <v>17</v>
@@ -27114,10 +27120,10 @@
     </row>
     <row r="738" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C738" s="1" t="n">
         <v>4118</v>
@@ -27132,7 +27138,7 @@
         <v>267</v>
       </c>
       <c r="G738" s="1" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H738" s="1" t="s">
         <v>17</v>
@@ -27143,7 +27149,7 @@
     </row>
     <row r="739" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B739" s="1" t="s">
         <v>878</v>
@@ -27172,10 +27178,10 @@
     </row>
     <row r="740" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C740" s="1" t="n">
         <v>4120</v>
@@ -27187,10 +27193,10 @@
         <v>10</v>
       </c>
       <c r="F740" s="3" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="G740" s="1" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H740" s="1" t="s">
         <v>17</v>
@@ -27201,13 +27207,13 @@
     </row>
     <row r="741" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B741" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C741" s="1" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="G741" s="1" t="s">
         <v>120</v>
@@ -27215,7 +27221,7 @@
     </row>
     <row r="742" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B742" s="1" t="s">
         <v>442</v>
@@ -27235,7 +27241,7 @@
     </row>
     <row r="743" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B743" s="1" t="s">
         <v>219</v>
@@ -27264,7 +27270,7 @@
     </row>
     <row r="744" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B744" s="1" t="s">
         <v>222</v>
@@ -27293,10 +27299,10 @@
     </row>
     <row r="745" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C745" s="1" t="n">
         <v>4202</v>
@@ -27322,7 +27328,7 @@
     </row>
     <row r="746" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B746" s="1" t="s">
         <v>1198</v>
@@ -27351,10 +27357,10 @@
     </row>
     <row r="747" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C747" s="1" t="n">
         <v>4204</v>
@@ -27369,7 +27375,7 @@
         <v>1098</v>
       </c>
       <c r="G747" s="1" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H747" s="1" t="s">
         <v>17</v>
@@ -27380,7 +27386,7 @@
     </row>
     <row r="748" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B748" s="1" t="s">
         <v>543</v>
@@ -27409,7 +27415,7 @@
     </row>
     <row r="749" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B749" s="1" t="s">
         <v>545</v>
@@ -27438,10 +27444,10 @@
     </row>
     <row r="750" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B750" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C750" s="1" t="n">
         <v>4208</v>
@@ -27467,10 +27473,10 @@
     </row>
     <row r="751" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C751" s="1" t="n">
         <v>4209</v>
@@ -27496,7 +27502,7 @@
     </row>
     <row r="752" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B752" s="1" t="s">
         <v>553</v>
@@ -27525,7 +27531,7 @@
     </row>
     <row r="753" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B753" s="1" t="s">
         <v>555</v>
@@ -27554,13 +27560,13 @@
     </row>
     <row r="754" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B754" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C754" s="20" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="G754" s="1" t="s">
         <v>120</v>
@@ -27568,7 +27574,7 @@
     </row>
     <row r="755" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B755" s="1" t="s">
         <v>442</v>
@@ -27588,7 +27594,7 @@
     </row>
     <row r="756" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B756" s="1" t="s">
         <v>219</v>
@@ -27617,7 +27623,7 @@
     </row>
     <row r="757" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B757" s="1" t="s">
         <v>222</v>
@@ -27646,10 +27652,10 @@
     </row>
     <row r="758" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C758" s="1" t="n">
         <v>4302</v>
@@ -27675,7 +27681,7 @@
     </row>
     <row r="759" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B759" s="1" t="s">
         <v>1198</v>
@@ -27704,10 +27710,10 @@
     </row>
     <row r="760" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C760" s="1" t="n">
         <v>4304</v>
@@ -27722,7 +27728,7 @@
         <v>1098</v>
       </c>
       <c r="G760" s="1" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H760" s="1" t="s">
         <v>17</v>
@@ -27733,7 +27739,7 @@
     </row>
     <row r="761" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B761" s="1" t="s">
         <v>543</v>
@@ -27762,7 +27768,7 @@
     </row>
     <row r="762" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B762" s="1" t="s">
         <v>545</v>
@@ -27791,10 +27797,10 @@
     </row>
     <row r="763" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B763" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C763" s="1" t="n">
         <v>4308</v>
@@ -27820,10 +27826,10 @@
     </row>
     <row r="764" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B764" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C764" s="1" t="n">
         <v>4309</v>
@@ -27849,7 +27855,7 @@
     </row>
     <row r="765" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B765" s="1" t="s">
         <v>553</v>
@@ -27878,7 +27884,7 @@
     </row>
     <row r="766" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B766" s="1" t="s">
         <v>555</v>
@@ -27907,13 +27913,13 @@
     </row>
     <row r="767" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B767" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C767" s="20" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="G767" s="1" t="s">
         <v>120</v>
@@ -27921,7 +27927,7 @@
     </row>
     <row r="768" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B768" s="1" t="s">
         <v>442</v>
@@ -27941,7 +27947,7 @@
     </row>
     <row r="769" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B769" s="1" t="s">
         <v>219</v>
@@ -27970,7 +27976,7 @@
     </row>
     <row r="770" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B770" s="1" t="s">
         <v>222</v>
@@ -27999,10 +28005,10 @@
     </row>
     <row r="771" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C771" s="1" t="n">
         <v>4402</v>
@@ -28028,7 +28034,7 @@
     </row>
     <row r="772" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B772" s="1" t="s">
         <v>1198</v>
@@ -28057,10 +28063,10 @@
     </row>
     <row r="773" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C773" s="1" t="n">
         <v>4404</v>
@@ -28075,7 +28081,7 @@
         <v>1098</v>
       </c>
       <c r="G773" s="1" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H773" s="1" t="s">
         <v>17</v>
@@ -28086,10 +28092,10 @@
     </row>
     <row r="774" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C774" s="1" t="n">
         <v>4406</v>
@@ -28104,7 +28110,7 @@
         <v>1098</v>
       </c>
       <c r="G774" s="1" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H774" s="1" t="s">
         <v>17</v>
@@ -28115,7 +28121,7 @@
     </row>
     <row r="775" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B775" s="1" t="s">
         <v>543</v>
@@ -28139,12 +28145,12 @@
         <v>17</v>
       </c>
       <c r="I775" s="1" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="776" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B776" s="1" t="s">
         <v>545</v>
@@ -28168,15 +28174,15 @@
         <v>17</v>
       </c>
       <c r="I776" s="1" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="777" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C777" s="1" t="n">
         <v>4410</v>
@@ -28202,10 +28208,10 @@
     </row>
     <row r="778" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C778" s="1" t="n">
         <v>4411</v>
@@ -28231,7 +28237,7 @@
     </row>
     <row r="779" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B779" s="1" t="s">
         <v>553</v>
@@ -28260,7 +28266,7 @@
     </row>
     <row r="780" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B780" s="1" t="s">
         <v>555</v>
@@ -28289,13 +28295,13 @@
     </row>
     <row r="781" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B781" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C781" s="20" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="G781" s="1" t="s">
         <v>120</v>
@@ -28303,7 +28309,7 @@
     </row>
     <row r="782" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B782" s="1" t="s">
         <v>442</v>
@@ -28323,7 +28329,7 @@
     </row>
     <row r="783" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B783" s="1" t="s">
         <v>161</v>
@@ -28341,7 +28347,7 @@
         <v>89</v>
       </c>
       <c r="G783" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H783" s="1" t="s">
         <v>17</v>
@@ -28352,7 +28358,7 @@
     </row>
     <row r="784" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>164</v>
@@ -28370,7 +28376,7 @@
         <v>89</v>
       </c>
       <c r="G784" s="1" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H784" s="1" t="s">
         <v>17</v>
@@ -28381,7 +28387,7 @@
     </row>
     <row r="785" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B785" s="1" t="s">
         <v>166</v>
@@ -28399,7 +28405,7 @@
         <v>89</v>
       </c>
       <c r="G785" s="1" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H785" s="1" t="s">
         <v>17</v>
@@ -28410,7 +28416,7 @@
     </row>
     <row r="786" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B786" s="1" t="s">
         <v>168</v>
@@ -28428,7 +28434,7 @@
         <v>89</v>
       </c>
       <c r="G786" s="1" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H786" s="1" t="s">
         <v>17</v>
@@ -28439,7 +28445,7 @@
     </row>
     <row r="787" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B787" s="1" t="s">
         <v>172</v>
@@ -28457,7 +28463,7 @@
         <v>89</v>
       </c>
       <c r="G787" s="1" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H787" s="1" t="s">
         <v>17</v>
@@ -28468,7 +28474,7 @@
     </row>
     <row r="788" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B788" s="1" t="s">
         <v>174</v>
@@ -28486,7 +28492,7 @@
         <v>89</v>
       </c>
       <c r="G788" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H788" s="1" t="s">
         <v>17</v>
@@ -28497,10 +28503,10 @@
     </row>
     <row r="789" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C789" s="1" t="n">
         <v>4506</v>
@@ -28509,13 +28515,13 @@
         <v>59</v>
       </c>
       <c r="E789" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F789" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G789" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H789" s="1" t="s">
         <v>17</v>
@@ -28526,10 +28532,10 @@
     </row>
     <row r="790" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="C790" s="1" t="n">
         <v>4507</v>
@@ -28538,13 +28544,13 @@
         <v>59</v>
       </c>
       <c r="E790" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F790" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G790" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H790" s="1" t="s">
         <v>17</v>
@@ -28555,10 +28561,10 @@
     </row>
     <row r="791" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C791" s="1" t="n">
         <v>4508</v>
@@ -28567,13 +28573,13 @@
         <v>59</v>
       </c>
       <c r="E791" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F791" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G791" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H791" s="1" t="s">
         <v>17</v>
@@ -28584,10 +28590,10 @@
     </row>
     <row r="792" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C792" s="1" t="n">
         <v>4509</v>
@@ -28599,7 +28605,7 @@
         <v>100</v>
       </c>
       <c r="G792" s="1" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H792" s="1" t="s">
         <v>17</v>
@@ -28610,7 +28616,7 @@
     </row>
     <row r="793" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B793" s="1" t="s">
         <v>193</v>
@@ -28639,7 +28645,7 @@
     </row>
     <row r="794" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B794" s="1" t="s">
         <v>195</v>
@@ -28668,7 +28674,7 @@
     </row>
     <row r="795" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B795" s="1" t="s">
         <v>197</v>
@@ -28697,7 +28703,7 @@
     </row>
     <row r="796" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B796" s="1" t="s">
         <v>199</v>
@@ -28726,7 +28732,7 @@
     </row>
     <row r="797" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B797" s="1" t="s">
         <v>202</v>
@@ -28755,7 +28761,7 @@
     </row>
     <row r="798" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B798" s="1" t="s">
         <v>204</v>
@@ -28784,10 +28790,10 @@
     </row>
     <row r="799" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C799" s="1" t="n">
         <v>4516</v>
@@ -28796,7 +28802,7 @@
         <v>59</v>
       </c>
       <c r="E799" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F799" s="3" t="s">
         <v>185</v>
@@ -28813,10 +28819,10 @@
     </row>
     <row r="800" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C800" s="1" t="n">
         <v>4517</v>
@@ -28825,7 +28831,7 @@
         <v>59</v>
       </c>
       <c r="E800" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F800" s="3" t="s">
         <v>185</v>
@@ -28842,10 +28848,10 @@
     </row>
     <row r="801" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C801" s="1" t="n">
         <v>4518</v>
@@ -28854,7 +28860,7 @@
         <v>59</v>
       </c>
       <c r="E801" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F801" s="3" t="s">
         <v>185</v>
@@ -28871,7 +28877,7 @@
     </row>
     <row r="802" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B802" s="1" t="s">
         <v>206</v>
@@ -28900,10 +28906,10 @@
     </row>
     <row r="803" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C803" s="1" t="n">
         <v>4520</v>
@@ -28918,7 +28924,7 @@
         <v>267</v>
       </c>
       <c r="G803" s="1" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H803" s="1" t="s">
         <v>17</v>
@@ -28929,10 +28935,10 @@
     </row>
     <row r="804" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C804" s="1" t="n">
         <v>4521</v>
@@ -28947,7 +28953,7 @@
         <v>267</v>
       </c>
       <c r="G804" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H804" s="1" t="s">
         <v>17</v>
@@ -28958,10 +28964,10 @@
     </row>
     <row r="805" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C805" s="1" t="n">
         <v>4522</v>
@@ -28976,7 +28982,7 @@
         <v>89</v>
       </c>
       <c r="G805" s="1" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H805" s="1" t="s">
         <v>23</v>
@@ -28987,10 +28993,10 @@
     </row>
     <row r="806" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C806" s="1" t="n">
         <v>4523</v>
@@ -29005,7 +29011,7 @@
         <v>89</v>
       </c>
       <c r="G806" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H806" s="1" t="s">
         <v>23</v>
@@ -29016,7 +29022,7 @@
     </row>
     <row r="807" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B807" s="1" t="s">
         <v>225</v>
@@ -29045,10 +29051,10 @@
     </row>
     <row r="808" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C808" s="1" t="n">
         <v>4525</v>
@@ -29074,7 +29080,7 @@
     </row>
     <row r="809" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B809" s="1" t="s">
         <v>219</v>
@@ -29103,7 +29109,7 @@
     </row>
     <row r="810" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B810" s="1" t="s">
         <v>222</v>
@@ -29132,7 +29138,7 @@
     </row>
     <row r="811" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B811" s="1" t="s">
         <v>309</v>
@@ -29161,10 +29167,10 @@
     </row>
     <row r="812" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C812" s="1" t="n">
         <v>4529</v>
@@ -29190,10 +29196,10 @@
     </row>
     <row r="813" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C813" s="1" t="n">
         <v>4530</v>
@@ -29214,15 +29220,15 @@
         <v>17</v>
       </c>
       <c r="I813" s="1" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="814" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C814" s="1" t="n">
         <v>4531</v>
@@ -29248,7 +29254,7 @@
     </row>
     <row r="815" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B815" s="1" t="s">
         <v>242</v>
@@ -29277,7 +29283,7 @@
     </row>
     <row r="816" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B816" s="1" t="s">
         <v>545</v>
@@ -29306,7 +29312,7 @@
     </row>
     <row r="817" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B817" s="1" t="s">
         <v>1084</v>
@@ -29335,10 +29341,10 @@
     </row>
     <row r="818" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C818" s="1" t="n">
         <v>4535</v>
@@ -29364,7 +29370,7 @@
     </row>
     <row r="819" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B819" s="1" t="s">
         <v>543</v>
@@ -29393,7 +29399,7 @@
     </row>
     <row r="820" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B820" s="1" t="s">
         <v>1087</v>
@@ -29422,7 +29428,7 @@
     </row>
     <row r="821" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B821" s="1" t="s">
         <v>247</v>
@@ -29451,10 +29457,10 @@
     </row>
     <row r="822" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C822" s="1" t="n">
         <v>4539</v>
@@ -29480,7 +29486,7 @@
     </row>
     <row r="823" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B823" s="1" t="s">
         <v>698</v>
@@ -29509,7 +29515,7 @@
     </row>
     <row r="824" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B824" s="1" t="s">
         <v>701</v>
@@ -29538,10 +29544,10 @@
     </row>
     <row r="825" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="C825" s="1" t="n">
         <v>4542</v>
@@ -29567,7 +29573,7 @@
     </row>
     <row r="826" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B826" s="1" t="s">
         <v>704</v>
@@ -29596,7 +29602,7 @@
     </row>
     <row r="827" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B827" s="1" t="s">
         <v>671</v>
@@ -29625,7 +29631,7 @@
     </row>
     <row r="828" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B828" s="1" t="s">
         <v>695</v>
@@ -29654,10 +29660,10 @@
     </row>
     <row r="829" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C829" s="1" t="n">
         <v>4546</v>
@@ -29683,10 +29689,10 @@
     </row>
     <row r="830" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C830" s="1" t="n">
         <v>4548</v>
@@ -29712,10 +29718,10 @@
     </row>
     <row r="831" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="C831" s="1" t="n">
         <v>4550</v>
@@ -29741,10 +29747,10 @@
     </row>
     <row r="832" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C832" s="1" t="n">
         <v>4552</v>
@@ -29770,10 +29776,10 @@
     </row>
     <row r="833" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C833" s="1" t="n">
         <v>4554</v>
@@ -29799,10 +29805,10 @@
     </row>
     <row r="834" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="C834" s="1" t="n">
         <v>4556</v>
@@ -29828,10 +29834,10 @@
     </row>
     <row r="835" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C835" s="1" t="n">
         <v>4558</v>
@@ -29857,10 +29863,10 @@
     </row>
     <row r="836" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="C836" s="1" t="n">
         <v>4560</v>
@@ -29886,7 +29892,7 @@
     </row>
     <row r="837" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B837" s="1" t="s">
         <v>370</v>
@@ -29915,7 +29921,7 @@
     </row>
     <row r="838" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B838" s="1" t="s">
         <v>1099</v>
@@ -29944,10 +29950,10 @@
     </row>
     <row r="839" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="C839" s="1" t="n">
         <v>4566</v>
@@ -29962,7 +29968,7 @@
         <v>349</v>
       </c>
       <c r="G839" s="1" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H839" s="1" t="s">
         <v>17</v>
@@ -29973,10 +29979,10 @@
     </row>
     <row r="840" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C840" s="1" t="n">
         <v>4568</v>
@@ -29991,7 +29997,7 @@
         <v>349</v>
       </c>
       <c r="G840" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H840" s="1" t="s">
         <v>17</v>
@@ -30002,7 +30008,7 @@
     </row>
     <row r="841" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B841" s="1" t="s">
         <v>1100</v>
@@ -30031,7 +30037,7 @@
     </row>
     <row r="842" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B842" s="1" t="s">
         <v>1102</v>
@@ -30060,7 +30066,7 @@
     </row>
     <row r="843" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B843" s="1" t="s">
         <v>683</v>
@@ -30089,7 +30095,7 @@
     </row>
     <row r="844" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B844" s="1" t="s">
         <v>686</v>
@@ -30118,7 +30124,7 @@
     </row>
     <row r="845" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B845" s="1" t="s">
         <v>689</v>
@@ -30147,7 +30153,7 @@
     </row>
     <row r="846" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B846" s="1" t="s">
         <v>692</v>
@@ -30176,7 +30182,7 @@
     </row>
     <row r="847" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B847" s="1" t="s">
         <v>716</v>
@@ -30205,7 +30211,7 @@
     </row>
     <row r="848" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B848" s="1" t="s">
         <v>718</v>
@@ -30234,7 +30240,7 @@
     </row>
     <row r="849" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B849" s="1" t="s">
         <v>720</v>
@@ -30263,7 +30269,7 @@
     </row>
     <row r="850" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B850" s="1" t="s">
         <v>722</v>
@@ -30292,7 +30298,7 @@
     </row>
     <row r="851" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B851" s="1" t="s">
         <v>724</v>
@@ -30321,7 +30327,7 @@
     </row>
     <row r="852" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B852" s="1" t="s">
         <v>726</v>
@@ -30350,7 +30356,7 @@
     </row>
     <row r="853" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B853" s="1" t="s">
         <v>728</v>
@@ -30379,7 +30385,7 @@
     </row>
     <row r="854" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B854" s="1" t="s">
         <v>730</v>
@@ -30408,7 +30414,7 @@
     </row>
     <row r="855" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B855" s="1" t="s">
         <v>732</v>
@@ -30437,7 +30443,7 @@
     </row>
     <row r="856" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B856" s="1" t="s">
         <v>734</v>
@@ -30466,7 +30472,7 @@
     </row>
     <row r="857" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B857" s="1" t="s">
         <v>736</v>
@@ -30495,7 +30501,7 @@
     </row>
     <row r="858" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B858" s="1" t="s">
         <v>738</v>
@@ -30524,7 +30530,7 @@
     </row>
     <row r="859" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B859" s="1" t="s">
         <v>740</v>
@@ -30553,7 +30559,7 @@
     </row>
     <row r="860" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B860" s="1" t="s">
         <v>742</v>
@@ -30582,7 +30588,7 @@
     </row>
     <row r="861" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B861" s="1" t="s">
         <v>744</v>
@@ -30611,7 +30617,7 @@
     </row>
     <row r="862" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B862" s="1" t="s">
         <v>746</v>
@@ -30640,7 +30646,7 @@
     </row>
     <row r="863" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B863" s="1" t="s">
         <v>707</v>
@@ -30669,7 +30675,7 @@
     </row>
     <row r="864" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B864" s="1" t="s">
         <v>709</v>
@@ -30698,7 +30704,7 @@
     </row>
     <row r="865" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B865" s="1" t="s">
         <v>711</v>
@@ -30727,7 +30733,7 @@
     </row>
     <row r="866" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B866" s="1" t="s">
         <v>713</v>
@@ -30756,7 +30762,7 @@
     </row>
     <row r="867" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B867" s="1" t="s">
         <v>748</v>
@@ -30785,7 +30791,7 @@
     </row>
     <row r="868" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B868" s="1" t="s">
         <v>750</v>
@@ -30814,7 +30820,7 @@
     </row>
     <row r="869" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B869" s="1" t="s">
         <v>752</v>
@@ -30843,7 +30849,7 @@
     </row>
     <row r="870" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B870" s="1" t="s">
         <v>754</v>
@@ -30872,7 +30878,7 @@
     </row>
     <row r="871" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B871" s="1" t="s">
         <v>1121</v>
@@ -30901,7 +30907,7 @@
     </row>
     <row r="872" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B872" s="1" t="s">
         <v>701</v>
@@ -30933,7 +30939,7 @@
     </row>
     <row r="873" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B873" s="1" t="s">
         <v>757</v>
@@ -30962,7 +30968,7 @@
     </row>
     <row r="874" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B874" s="1" t="s">
         <v>759</v>
@@ -30991,7 +30997,7 @@
     </row>
     <row r="875" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B875" s="1" t="s">
         <v>761</v>
@@ -31020,7 +31026,7 @@
     </row>
     <row r="876" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B876" s="1" t="s">
         <v>763</v>
@@ -31049,10 +31055,10 @@
     </row>
     <row r="877" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B877" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C877" s="1" t="n">
         <v>4609</v>
@@ -31067,21 +31073,21 @@
         <v>267</v>
       </c>
       <c r="G877" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H877" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I877" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="878" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C878" s="1" t="n">
         <v>4610</v>
@@ -31096,7 +31102,7 @@
         <v>143</v>
       </c>
       <c r="G878" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H878" s="1" t="s">
         <v>23</v>
@@ -31107,10 +31113,10 @@
     </row>
     <row r="879" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C879" s="1" t="n">
         <v>4612</v>
@@ -31125,21 +31131,21 @@
         <v>267</v>
       </c>
       <c r="G879" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H879" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I879" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="880" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="C880" s="1" t="n">
         <v>4613</v>
@@ -31154,21 +31160,21 @@
         <v>267</v>
       </c>
       <c r="G880" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H880" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I880" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="881" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C881" s="1" t="n">
         <v>4614</v>
@@ -31183,7 +31189,7 @@
         <v>267</v>
       </c>
       <c r="G881" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H881" s="1" t="s">
         <v>23</v>
@@ -31194,7 +31200,7 @@
     </row>
     <row r="882" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B882" s="1" t="s">
         <v>345</v>
@@ -31212,7 +31218,7 @@
         <v>267</v>
       </c>
       <c r="G882" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H882" s="1" t="s">
         <v>17</v>
@@ -31223,21 +31229,21 @@
     </row>
     <row r="883" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B883" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C883" s="20" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="884" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C884" s="1" t="n">
         <v>4620</v>
@@ -31252,7 +31258,7 @@
         <v>267</v>
       </c>
       <c r="G884" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H884" s="1" t="s">
         <v>17</v>
@@ -31263,7 +31269,7 @@
     </row>
     <row r="885" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B885" s="1" t="s">
         <v>120</v>
@@ -31277,7 +31283,7 @@
     </row>
     <row r="886" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B886" s="1" t="s">
         <v>442</v>
@@ -31297,7 +31303,7 @@
     </row>
     <row r="887" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B887" s="1" t="s">
         <v>765</v>
@@ -31326,7 +31332,7 @@
     </row>
     <row r="888" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B888" s="1" t="s">
         <v>768</v>
@@ -31355,7 +31361,7 @@
     </row>
     <row r="889" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B889" s="1" t="s">
         <v>770</v>
@@ -31384,7 +31390,7 @@
     </row>
     <row r="890" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B890" s="1" t="s">
         <v>772</v>
@@ -31413,10 +31419,10 @@
     </row>
     <row r="891" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B891" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C891" s="1" t="n">
         <v>4700</v>
@@ -31437,7 +31443,7 @@
         <v>17</v>
       </c>
       <c r="I891" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="892" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31445,7 +31451,7 @@
         <v>963</v>
       </c>
       <c r="B892" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C892" s="1" t="n">
         <v>4701</v>
@@ -31460,7 +31466,7 @@
         <v>267</v>
       </c>
       <c r="G892" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H892" s="1" t="s">
         <v>23</v>
@@ -31489,13 +31495,13 @@
         <v>267</v>
       </c>
       <c r="G893" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H893" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I893" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="894" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31503,7 +31509,7 @@
         <v>963</v>
       </c>
       <c r="B894" s="1" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C894" s="1" t="n">
         <v>4703</v>
@@ -31518,7 +31524,7 @@
         <v>101</v>
       </c>
       <c r="G894" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H894" s="1" t="s">
         <v>23</v>
@@ -31532,7 +31538,7 @@
         <v>963</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C895" s="1" t="n">
         <v>4704</v>
@@ -31547,7 +31553,7 @@
         <v>101</v>
       </c>
       <c r="G895" s="1" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H895" s="1" t="s">
         <v>23</v>
@@ -31558,7 +31564,7 @@
     </row>
     <row r="896" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B896" s="1" t="s">
         <v>1060</v>
@@ -31584,7 +31590,7 @@
     </row>
     <row r="897" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B897" s="1" t="s">
         <v>1091</v>
@@ -31610,7 +31616,7 @@
     </row>
     <row r="898" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B898" s="1" t="s">
         <v>695</v>
@@ -31639,7 +31645,7 @@
     </row>
     <row r="899" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B899" s="1" t="s">
         <v>219</v>
@@ -31668,7 +31674,7 @@
     </row>
     <row r="900" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B900" s="1" t="s">
         <v>222</v>
@@ -31697,7 +31703,7 @@
     </row>
     <row r="901" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B901" s="1" t="s">
         <v>309</v>
@@ -31726,10 +31732,10 @@
     </row>
     <row r="902" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C902" s="1" t="n">
         <v>4807</v>
@@ -31755,7 +31761,7 @@
     </row>
     <row r="903" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B903" s="1" t="s">
         <v>377</v>
@@ -31779,15 +31785,15 @@
         <v>17</v>
       </c>
       <c r="I903" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="904" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B904" s="1" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C904" s="1" t="n">
         <v>4809</v>
@@ -31802,7 +31808,7 @@
         <v>220</v>
       </c>
       <c r="G904" s="1" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H904" s="1" t="s">
         <v>17</v>
@@ -31813,10 +31819,10 @@
     </row>
     <row r="905" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B905" s="1" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C905" s="1" t="n">
         <v>4810</v>
@@ -31831,7 +31837,7 @@
         <v>267</v>
       </c>
       <c r="G905" s="1" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H905" s="1" t="s">
         <v>17</v>
@@ -31842,10 +31848,10 @@
     </row>
     <row r="906" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C906" s="1" t="n">
         <v>4811</v>
@@ -31860,7 +31866,7 @@
         <v>89</v>
       </c>
       <c r="G906" s="1" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H906" s="1" t="s">
         <v>17</v>
@@ -31871,13 +31877,13 @@
     </row>
     <row r="907" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B907" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C907" s="20" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="G907" s="1" t="s">
         <v>120</v>
@@ -31885,7 +31891,7 @@
     </row>
     <row r="908" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B908" s="1" t="s">
         <v>442</v>
@@ -31905,10 +31911,10 @@
     </row>
     <row r="909" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B909" s="1" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C909" s="1" t="n">
         <v>4900</v>
@@ -31929,12 +31935,12 @@
         <v>17</v>
       </c>
       <c r="I909" s="1" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="910" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B910" s="1" t="s">
         <v>161</v>
@@ -31952,7 +31958,7 @@
         <v>89</v>
       </c>
       <c r="G910" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H910" s="1" t="s">
         <v>17</v>
@@ -31963,7 +31969,7 @@
     </row>
     <row r="911" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B911" s="1" t="s">
         <v>164</v>
@@ -31981,7 +31987,7 @@
         <v>89</v>
       </c>
       <c r="G911" s="1" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H911" s="1" t="s">
         <v>17</v>
@@ -31992,7 +31998,7 @@
     </row>
     <row r="912" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B912" s="1" t="s">
         <v>166</v>
@@ -32010,7 +32016,7 @@
         <v>89</v>
       </c>
       <c r="G912" s="1" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H912" s="1" t="s">
         <v>17</v>
@@ -32021,7 +32027,7 @@
     </row>
     <row r="913" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B913" s="1" t="s">
         <v>168</v>
@@ -32039,7 +32045,7 @@
         <v>89</v>
       </c>
       <c r="G913" s="1" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H913" s="1" t="s">
         <v>17</v>
@@ -32050,7 +32056,7 @@
     </row>
     <row r="914" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B914" s="1" t="s">
         <v>172</v>
@@ -32068,7 +32074,7 @@
         <v>89</v>
       </c>
       <c r="G914" s="1" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H914" s="1" t="s">
         <v>17</v>
@@ -32079,7 +32085,7 @@
     </row>
     <row r="915" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B915" s="1" t="s">
         <v>174</v>
@@ -32097,7 +32103,7 @@
         <v>89</v>
       </c>
       <c r="G915" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H915" s="1" t="s">
         <v>17</v>
@@ -32108,10 +32114,10 @@
     </row>
     <row r="916" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B916" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C916" s="1" t="n">
         <v>4907</v>
@@ -32120,13 +32126,13 @@
         <v>59</v>
       </c>
       <c r="E916" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F916" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G916" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H916" s="1" t="s">
         <v>17</v>
@@ -32137,10 +32143,10 @@
     </row>
     <row r="917" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B917" s="1" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="C917" s="1" t="n">
         <v>4908</v>
@@ -32149,13 +32155,13 @@
         <v>59</v>
       </c>
       <c r="E917" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F917" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G917" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H917" s="1" t="s">
         <v>17</v>
@@ -32166,10 +32172,10 @@
     </row>
     <row r="918" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B918" s="1" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C918" s="1" t="n">
         <v>4909</v>
@@ -32178,13 +32184,13 @@
         <v>59</v>
       </c>
       <c r="E918" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F918" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G918" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H918" s="1" t="s">
         <v>17</v>
@@ -32195,10 +32201,10 @@
     </row>
     <row r="919" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B919" s="1" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C919" s="1" t="n">
         <v>4910</v>
@@ -32213,7 +32219,7 @@
         <v>220</v>
       </c>
       <c r="G919" s="1" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H919" s="1" t="s">
         <v>17</v>
@@ -32224,7 +32230,7 @@
     </row>
     <row r="920" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B920" s="1" t="s">
         <v>193</v>
@@ -32253,7 +32259,7 @@
     </row>
     <row r="921" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B921" s="1" t="s">
         <v>195</v>
@@ -32282,7 +32288,7 @@
     </row>
     <row r="922" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B922" s="1" t="s">
         <v>197</v>
@@ -32311,7 +32317,7 @@
     </row>
     <row r="923" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B923" s="1" t="s">
         <v>199</v>
@@ -32340,7 +32346,7 @@
     </row>
     <row r="924" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B924" s="1" t="s">
         <v>202</v>
@@ -32369,7 +32375,7 @@
     </row>
     <row r="925" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B925" s="1" t="s">
         <v>204</v>
@@ -32398,10 +32404,10 @@
     </row>
     <row r="926" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B926" s="1" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C926" s="1" t="n">
         <v>4917</v>
@@ -32410,7 +32416,7 @@
         <v>59</v>
       </c>
       <c r="E926" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F926" s="3" t="s">
         <v>185</v>
@@ -32427,10 +32433,10 @@
     </row>
     <row r="927" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B927" s="1" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C927" s="1" t="n">
         <v>4918</v>
@@ -32439,7 +32445,7 @@
         <v>59</v>
       </c>
       <c r="E927" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F927" s="3" t="s">
         <v>185</v>
@@ -32456,10 +32462,10 @@
     </row>
     <row r="928" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B928" s="1" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C928" s="1" t="n">
         <v>4919</v>
@@ -32468,7 +32474,7 @@
         <v>59</v>
       </c>
       <c r="E928" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F928" s="3" t="s">
         <v>185</v>
@@ -32485,7 +32491,7 @@
     </row>
     <row r="929" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B929" s="1" t="s">
         <v>206</v>
@@ -32514,10 +32520,10 @@
     </row>
     <row r="930" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B930" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C930" s="1" t="n">
         <v>4921</v>
@@ -32532,7 +32538,7 @@
         <v>267</v>
       </c>
       <c r="G930" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H930" s="1" t="s">
         <v>23</v>
@@ -32543,10 +32549,10 @@
     </row>
     <row r="931" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B931" s="1" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C931" s="1" t="n">
         <v>4922</v>
@@ -32561,7 +32567,7 @@
         <v>143</v>
       </c>
       <c r="G931" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H931" s="1" t="s">
         <v>23</v>
@@ -32572,10 +32578,10 @@
     </row>
     <row r="932" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B932" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C932" s="1" t="n">
         <v>4924</v>
@@ -32590,21 +32596,21 @@
         <v>267</v>
       </c>
       <c r="G932" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H932" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I932" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="933" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B933" s="1" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C933" s="1" t="n">
         <v>4925</v>
@@ -32619,7 +32625,7 @@
         <v>267</v>
       </c>
       <c r="G933" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H933" s="1" t="s">
         <v>17</v>
@@ -32630,13 +32636,13 @@
     </row>
     <row r="934" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B934" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C934" s="20" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="G934" s="1" t="s">
         <v>120</v>
@@ -32644,7 +32650,7 @@
     </row>
     <row r="935" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B935" s="1" t="s">
         <v>1022</v>
@@ -32673,10 +32679,10 @@
     </row>
     <row r="936" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B936" s="1" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C936" s="1" t="n">
         <v>4930</v>
@@ -32702,10 +32708,10 @@
     </row>
     <row r="937" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B937" s="1" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C937" s="1" t="n">
         <v>4931</v>
@@ -32731,21 +32737,21 @@
     </row>
     <row r="938" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B938" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C938" s="20" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="939" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B939" s="1" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C939" s="1" t="n">
         <v>4940</v>
@@ -32757,10 +32763,10 @@
         <v>10</v>
       </c>
       <c r="F939" s="3" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G939" s="1" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H939" s="1" t="s">
         <v>23</v>
@@ -32771,10 +32777,10 @@
     </row>
     <row r="940" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B940" s="1" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C940" s="1" t="n">
         <v>4941</v>
@@ -32786,10 +32792,10 @@
         <v>10</v>
       </c>
       <c r="F940" s="3" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G940" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H940" s="1" t="s">
         <v>23</v>
@@ -32800,10 +32806,10 @@
     </row>
     <row r="941" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B941" s="1" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C941" s="1" t="n">
         <v>4942</v>
@@ -32815,10 +32821,10 @@
         <v>10</v>
       </c>
       <c r="F941" s="3" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G941" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H941" s="1" t="s">
         <v>23</v>
@@ -32829,13 +32835,13 @@
     </row>
     <row r="942" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B942" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C942" s="20" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="G942" s="1" t="s">
         <v>120</v>
@@ -32843,7 +32849,7 @@
     </row>
     <row r="943" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B943" s="1" t="s">
         <v>442</v>
@@ -32863,10 +32869,10 @@
     </row>
     <row r="944" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B944" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C944" s="1" t="n">
         <v>5200</v>
@@ -32889,7 +32895,7 @@
     </row>
     <row r="945" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B945" s="1" t="s">
         <v>1140</v>
@@ -32915,7 +32921,7 @@
     </row>
     <row r="946" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B946" s="1" t="s">
         <v>822</v>
@@ -32941,10 +32947,10 @@
     </row>
     <row r="947" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B947" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C947" s="1" t="n">
         <v>5203</v>
@@ -32967,7 +32973,7 @@
     </row>
     <row r="948" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B948" s="1" t="s">
         <v>1160</v>
@@ -32996,10 +33002,10 @@
     </row>
     <row r="949" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C949" s="1" t="n">
         <v>5205</v>
@@ -33020,15 +33026,15 @@
         <v>17</v>
       </c>
       <c r="I949" s="1" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="950" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C950" s="1" t="n">
         <v>5206</v>
@@ -33049,12 +33055,12 @@
         <v>17</v>
       </c>
       <c r="I950" s="1" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="951" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B951" s="1" t="s">
         <v>1146</v>
@@ -33083,10 +33089,10 @@
     </row>
     <row r="952" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B952" s="1" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C952" s="1" t="n">
         <v>5208</v>
@@ -33112,7 +33118,7 @@
     </row>
     <row r="953" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B953" s="1" t="s">
         <v>1168</v>
@@ -33124,7 +33130,7 @@
         <v>20</v>
       </c>
       <c r="E953" s="1" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="F953" s="3" t="s">
         <v>326</v>
@@ -33136,12 +33142,12 @@
         <v>17</v>
       </c>
       <c r="I953" s="1" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="954" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B954" s="1" t="s">
         <v>1152</v>
@@ -33170,10 +33176,10 @@
     </row>
     <row r="955" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B955" s="1" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C955" s="1" t="n">
         <v>5211</v>
@@ -33199,7 +33205,7 @@
     </row>
     <row r="956" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B956" s="1" t="s">
         <v>1156</v>
@@ -33228,7 +33234,7 @@
     </row>
     <row r="957" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B957" s="1" t="s">
         <v>526</v>
@@ -33252,12 +33258,12 @@
         <v>17</v>
       </c>
       <c r="I957" s="1" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="958" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B958" s="1" t="s">
         <v>1164</v>
@@ -33286,10 +33292,10 @@
     </row>
     <row r="959" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B959" s="1" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C959" s="1" t="n">
         <v>5215</v>
@@ -33304,7 +33310,7 @@
         <v>94</v>
       </c>
       <c r="G959" s="1" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H959" s="1" t="s">
         <v>17</v>
@@ -33315,7 +33321,7 @@
     </row>
     <row r="960" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B960" s="1" t="s">
         <v>1168</v>
@@ -33344,7 +33350,7 @@
     </row>
     <row r="961" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B961" s="1" t="s">
         <v>120</v>
@@ -33367,7 +33373,7 @@
     </row>
     <row r="962" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B962" s="1" t="s">
         <v>1171</v>
@@ -33393,7 +33399,7 @@
     </row>
     <row r="963" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B963" s="1" t="s">
         <v>1176</v>
@@ -33416,7 +33422,7 @@
     </row>
     <row r="964" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B964" s="1" t="s">
         <v>1178</v>
@@ -33439,7 +33445,7 @@
     </row>
     <row r="965" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B965" s="1" t="s">
         <v>1180</v>
@@ -33462,7 +33468,7 @@
     </row>
     <row r="966" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B966" s="1" t="s">
         <v>1182</v>
@@ -33485,7 +33491,7 @@
     </row>
     <row r="967" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B967" s="1" t="s">
         <v>1184</v>
@@ -33508,7 +33514,7 @@
     </row>
     <row r="968" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B968" s="1" t="s">
         <v>1186</v>
@@ -33531,7 +33537,7 @@
     </row>
     <row r="969" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B969" s="1" t="s">
         <v>1188</v>
@@ -33554,13 +33560,13 @@
     </row>
     <row r="970" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B970" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C970" s="20" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G970" s="1" t="s">
         <v>120</v>
@@ -33568,7 +33574,7 @@
     </row>
     <row r="971" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B971" s="1" t="s">
         <v>442</v>
@@ -33591,7 +33597,7 @@
         <v>12</v>
       </c>
       <c r="B972" s="1" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C972" s="1" t="n">
         <v>5400</v>
@@ -33606,13 +33612,13 @@
         <v>267</v>
       </c>
       <c r="G972" s="1" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H972" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I972" s="1" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="973" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33620,7 +33626,7 @@
         <v>12</v>
       </c>
       <c r="B973" s="1" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C973" s="1" t="n">
         <v>5401</v>
@@ -33635,7 +33641,7 @@
         <v>267</v>
       </c>
       <c r="G973" s="1" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H973" s="1" t="s">
         <v>17</v>
@@ -33649,7 +33655,7 @@
         <v>12</v>
       </c>
       <c r="B974" s="1" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C974" s="1" t="n">
         <v>5402</v>
@@ -33664,13 +33670,13 @@
         <v>267</v>
       </c>
       <c r="G974" s="1" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H974" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I974" s="1" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="975" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33678,7 +33684,7 @@
         <v>12</v>
       </c>
       <c r="B975" s="23" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C975" s="1" t="n">
         <v>5403</v>
@@ -33690,10 +33696,10 @@
         <v>0.1</v>
       </c>
       <c r="F975" s="3" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="G975" s="1" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H975" s="1" t="s">
         <v>17</v>
@@ -33719,13 +33725,13 @@
         <v>267</v>
       </c>
       <c r="G976" s="1" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H976" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I976" s="1" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="977" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33733,7 +33739,7 @@
         <v>12</v>
       </c>
       <c r="B977" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C977" s="1" t="n">
         <v>5405</v>
@@ -33748,13 +33754,13 @@
         <v>267</v>
       </c>
       <c r="G977" s="1" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H977" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I977" s="1" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="978" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33762,7 +33768,7 @@
         <v>12</v>
       </c>
       <c r="B978" s="1" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C978" s="1" t="n">
         <v>5406</v>
@@ -33777,13 +33783,13 @@
         <v>267</v>
       </c>
       <c r="G978" s="1" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H978" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I978" s="1" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="979" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33791,7 +33797,7 @@
         <v>12</v>
       </c>
       <c r="B979" s="1" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C979" s="1" t="n">
         <v>5407</v>
@@ -33806,7 +33812,7 @@
         <v>267</v>
       </c>
       <c r="G979" s="1" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H979" s="1" t="s">
         <v>17</v>
@@ -33820,7 +33826,7 @@
         <v>963</v>
       </c>
       <c r="B980" s="1" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C980" s="1" t="n">
         <v>5420</v>
@@ -33835,7 +33841,7 @@
         <v>89</v>
       </c>
       <c r="G980" s="1" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H980" s="1" t="s">
         <v>23</v>
@@ -33849,7 +33855,7 @@
         <v>963</v>
       </c>
       <c r="B981" s="1" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C981" s="1" t="n">
         <v>5421</v>
@@ -33864,13 +33870,13 @@
         <v>267</v>
       </c>
       <c r="G981" s="1" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H981" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I981" s="1" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="982" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33878,7 +33884,7 @@
         <v>963</v>
       </c>
       <c r="B982" s="1" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C982" s="1" t="n">
         <v>5422</v>
@@ -33893,13 +33899,13 @@
         <v>267</v>
       </c>
       <c r="G982" s="1" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H982" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I982" s="1" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="983" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33907,7 +33913,7 @@
         <v>963</v>
       </c>
       <c r="B983" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="C983" s="1" t="n">
         <v>5423</v>
@@ -33922,13 +33928,13 @@
         <v>267</v>
       </c>
       <c r="G983" s="1" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H983" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I983" s="1" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="984" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33936,7 +33942,7 @@
         <v>963</v>
       </c>
       <c r="B984" s="1" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C984" s="1" t="n">
         <v>5424</v>
@@ -33951,7 +33957,7 @@
         <v>267</v>
       </c>
       <c r="G984" s="1" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H984" s="1" t="s">
         <v>23</v>
@@ -33965,7 +33971,7 @@
         <v>963</v>
       </c>
       <c r="B985" s="1" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C985" s="1" t="n">
         <v>5425</v>
@@ -33980,13 +33986,13 @@
         <v>267</v>
       </c>
       <c r="G985" s="1" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H985" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I985" s="1" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="986" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33994,7 +34000,7 @@
         <v>963</v>
       </c>
       <c r="B986" s="1" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C986" s="1" t="n">
         <v>5426</v>
@@ -34009,13 +34015,13 @@
         <v>267</v>
       </c>
       <c r="G986" s="1" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H986" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I986" s="1" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="987" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34023,7 +34029,7 @@
         <v>963</v>
       </c>
       <c r="B987" s="1" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C987" s="1" t="n">
         <v>5427</v>
@@ -34038,7 +34044,7 @@
         <v>267</v>
       </c>
       <c r="G987" s="1" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H987" s="1" t="s">
         <v>23</v>
@@ -34052,7 +34058,7 @@
         <v>963</v>
       </c>
       <c r="B988" s="1" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C988" s="1" t="n">
         <v>5428</v>
@@ -34067,7 +34073,7 @@
         <v>143</v>
       </c>
       <c r="G988" s="1" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H988" s="1" t="s">
         <v>23</v>
@@ -34078,7 +34084,7 @@
         <v>963</v>
       </c>
       <c r="B989" s="1" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C989" s="1" t="n">
         <v>5430</v>
@@ -34093,18 +34099,18 @@
         <v>267</v>
       </c>
       <c r="G989" s="1" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H989" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I989" s="1" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="990" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B990" s="1" t="s">
         <v>1060</v>
@@ -34130,10 +34136,10 @@
     </row>
     <row r="991" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B991" s="1" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="C991" s="1" t="n">
         <v>5501</v>
@@ -34154,15 +34160,15 @@
         <v>17</v>
       </c>
       <c r="I991" s="1" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="992" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B992" s="1" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C992" s="1" t="n">
         <v>5502</v>
@@ -34188,10 +34194,10 @@
     </row>
     <row r="993" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C993" s="1" t="n">
         <v>5504</v>
@@ -34217,10 +34223,10 @@
     </row>
     <row r="994" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B994" s="1" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C994" s="1" t="n">
         <v>5506</v>
@@ -34246,10 +34252,10 @@
     </row>
     <row r="995" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B995" s="1" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="C995" s="1" t="n">
         <v>5507</v>
@@ -34264,7 +34270,7 @@
         <v>94</v>
       </c>
       <c r="G995" s="1" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H995" s="1" t="s">
         <v>17</v>
@@ -34275,13 +34281,13 @@
     </row>
     <row r="996" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B996" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C996" s="20" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="G996" s="1" t="s">
         <v>120</v>
@@ -34289,7 +34295,7 @@
     </row>
     <row r="997" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B997" s="1" t="s">
         <v>442</v>
@@ -34312,7 +34318,7 @@
         <v>963</v>
       </c>
       <c r="B998" s="1" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C998" s="1" t="n">
         <v>5700</v>
@@ -34321,7 +34327,7 @@
         <v>443</v>
       </c>
       <c r="G998" s="1" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H998" s="1" t="s">
         <v>23</v>
@@ -34329,10 +34335,10 @@
     </row>
     <row r="999" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B999" s="1" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C999" s="1" t="n">
         <v>5800</v>
@@ -34347,21 +34353,21 @@
         <v>267</v>
       </c>
       <c r="G999" s="1" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H999" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I999" s="1" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1000" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1000" s="1" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C1000" s="1" t="n">
         <v>5801</v>
@@ -34376,21 +34382,21 @@
         <v>267</v>
       </c>
       <c r="G1000" s="1" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H1000" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I1000" s="1" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1001" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1001" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1001" s="1" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C1001" s="1" t="n">
         <v>5802</v>
@@ -34405,32 +34411,32 @@
         <v>267</v>
       </c>
       <c r="G1001" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H1001" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I1001" s="1" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1002" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1002" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1002" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C1002" s="20" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1003" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1003" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1003" s="1" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C1003" s="1" t="n">
         <v>5810</v>
@@ -34445,21 +34451,21 @@
         <v>267</v>
       </c>
       <c r="G1003" s="1" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H1003" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I1003" s="1" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1004" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1004" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1004" s="1" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C1004" s="1" t="n">
         <v>5811</v>
@@ -34474,21 +34480,21 @@
         <v>267</v>
       </c>
       <c r="G1004" s="1" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H1004" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I1004" s="1" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1005" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1005" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1005" s="1" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C1005" s="1" t="n">
         <v>5812</v>
@@ -34503,24 +34509,24 @@
         <v>267</v>
       </c>
       <c r="G1005" s="1" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H1005" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I1005" s="1" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1006" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1006" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1006" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C1006" s="20" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -34563,7 +34569,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -34573,7 +34579,7 @@
     </row>
     <row r="2" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -34588,7 +34594,7 @@
     </row>
     <row r="4" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -34608,13 +34614,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34625,7 +34631,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34788,7 +34794,7 @@
         <v>277</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34799,7 +34805,7 @@
         <v>278</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34810,7 +34816,7 @@
         <v>512</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34821,7 +34827,7 @@
         <v>279</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34832,7 +34838,7 @@
         <v>276</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34843,7 +34849,7 @@
         <v>275</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34854,7 +34860,7 @@
         <v>274</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34865,7 +34871,7 @@
         <v>273</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34876,7 +34882,7 @@
         <v>295</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34887,7 +34893,7 @@
         <v>294</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34898,7 +34904,7 @@
         <v>293</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34909,7 +34915,7 @@
         <v>296</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34920,7 +34926,7 @@
         <v>292</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34931,7 +34937,7 @@
         <v>291</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34942,7 +34948,7 @@
         <v>290</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34953,7 +34959,7 @@
         <v>289</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34964,7 +34970,7 @@
         <v>288</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34975,7 +34981,7 @@
         <v>261</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34986,7 +34992,7 @@
         <v>260</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35006,7 +35012,7 @@
         <v>258</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35017,7 +35023,7 @@
         <v>257</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35028,7 +35034,7 @@
         <v>256</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -35073,1125 +35079,1130 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C39" s="29" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="1" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="1" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="1" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="1" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="1" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="1" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="1" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="1" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="1" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="1" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="1" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="1" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="1" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="1" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="1" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="1" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="1" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="1" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="1" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="1" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="1" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="1" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="1" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="1" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="1" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="1" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="1" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="1" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="1" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="1" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="1" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="1" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="1" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B128" s="1" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="1" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="1" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="1" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="1" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="1" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="1" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="1" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B138" s="1" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="1" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B141" s="1" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B142" s="1" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B143" s="1" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="1" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B145" s="1" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B146" s="1" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B148" s="1" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B149" s="1" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B150" s="1" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B151" s="1" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B152" s="1" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B153" s="1" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B154" s="1" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B155" s="1" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B156" s="1" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B157" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B159" s="1" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B160" s="1" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="1" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B162" s="1" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B164" s="1" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B165" s="1" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B166" s="1" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B167" s="1" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B168" s="1" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B170" s="1" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B171" s="1" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B172" s="1" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B173" s="1" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B174" s="1" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B176" s="1" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B177" s="1" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B178" s="1" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B179" s="1" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B180" s="1" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B181" s="1" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="1" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B184" s="1" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B185" s="1" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B186" s="1" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B187" s="1" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B188" s="1" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B189" s="1" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B191" s="1" t="s">
-        <v>1802</v>
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="1" t="s">
+        <v>1804</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
